--- a/bom/Component_Base.xlsx
+++ b/bom/Component_Base.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="421">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">SMCJ26A (однонаправленный, 26 В, 1500 Вт)</t>
   </si>
   <si>
-    <t xml:space="preserve">Плата-носитель</t>
+    <t xml:space="preserve">PS</t>
   </si>
   <si>
     <t xml:space="preserve">доска + чат 15.09 (утверждено Mikhail)</t>
@@ -284,6 +284,9 @@
     <t xml:space="preserve">Логическая</t>
   </si>
   <si>
+    <t xml:space="preserve">MC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Отдельного компонента нет. Потребители: TCA9548A, подтяжки I2C/RST, подтяжка выхода оптрона KH (&lt;20 мА)</t>
   </si>
   <si>
@@ -329,7 +332,7 @@
     <t xml:space="preserve">доска + чат 15.09</t>
   </si>
   <si>
-    <t xml:space="preserve">Распиновка принята («Аккуратно!»); ПК — родной USB GPIO19/20, запас CH343 GPIO43/44; VIN от изолированных +5</t>
+    <t xml:space="preserve">Распиновка принята («Аккуратно!»); ПК — родной USB GPIO19/20, запас CH343 GPIO43/44; VIN от изолированных +5; GPIO48 — концевик M1 (предложение)</t>
   </si>
   <si>
     <t xml:space="preserve">E-021</t>
@@ -446,6 +449,9 @@
     <t xml:space="preserve">(6)</t>
   </si>
   <si>
+    <t xml:space="preserve">CH</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://ozon.ru/t/tPvFr4r</t>
   </si>
   <si>
@@ -662,7 +668,7 @@
     <t xml:space="preserve">доска + ChipDip</t>
   </si>
   <si>
-    <t xml:space="preserve">Катушки от шины KH (+5P), ~40 мА каждая</t>
+    <t xml:space="preserve">Катушки от шины KH (+5P), ~40 мА каждая; сторона — граница: катушки от +5P, контакты в логических цепях</t>
   </si>
   <si>
     <t xml:space="preserve">E-051</t>
@@ -674,6 +680,9 @@
     <t xml:space="preserve">(тип)</t>
   </si>
   <si>
+    <t xml:space="preserve">LR</t>
+  </si>
+  <si>
     <t xml:space="preserve">Раскладка 2×3: SCL, SDA, GND / IN1, IN2, пусто. Варианты (банан 4 мм, приборные, барьерные) отложены. Разъём на логической земле</t>
   </si>
   <si>
@@ -779,6 +788,9 @@
     <t xml:space="preserve">(13)</t>
   </si>
   <si>
+    <t xml:space="preserve">GR</t>
+  </si>
+  <si>
     <t xml:space="preserve">ТЗ v0.2</t>
   </si>
   <si>
@@ -830,7 +842,7 @@
     <t xml:space="preserve">20–22 AWG</t>
   </si>
   <si>
-    <t xml:space="preserve">Бухта</t>
+    <t xml:space="preserve">Бухта; Участок DC-гнездо → предохранитель → реле NRP-15 (полный ток 9,2 А) — 18 AWG (утверждено 16.09)</t>
   </si>
   <si>
     <t xml:space="preserve">E-082</t>
@@ -866,7 +878,16 @@
     <t xml:space="preserve">DC-гнездо питания на корпусе (вход 24 В от адаптера)</t>
   </si>
   <si>
-    <t xml:space="preserve">НАДО НАЙТИ: ответная часть к штекеру R7B адаптера GST (DIN 4-pin, Kycon KPPX-4P). Кандидаты: KPJX-4S-S (Kycon, ~560 ₽, chipdip) — без переделки адаптера; XT60E-F (~120 ₽) — с заменой штекера на кабеле адаптера. Ток ≥ 10 А, фиксация</t>
+    <t xml:space="preserve">Kycon KPJX-PM-4S — панельное гнездо 4-pin power mini-DIN, 7,5 А/контакт, 48 В; ответная часть к штекеру R7B адаптера</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.chipdip.ru/product/kpjx-pm-4s-dc-power-connectors-4-pn-panel-mt-mini-din-kycon-8005303752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чат 16.09 (утверждено Mikhail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кабель адаптера несъёмный, штекер R7B вставляется напрямую. +V и GND — по два контакта на полюс (распиновку сверить с PDF Kycon и спецификацией Mean Well). Срок поставки ChipDip 6–7 недель; проверить тип выводов (под пайку провода)</t>
   </si>
   <si>
     <t xml:space="preserve">E-015</t>
@@ -893,6 +914,54 @@
     <t xml:space="preserve">Функция и порог ~1 А утверждены; конкретная модель — кандидат. Требование внесено в ТЗ схвата v0.3</t>
   </si>
   <si>
+    <t xml:space="preserve">E-090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Концевой выключатель M1 — опорная метка нуля поворота платформы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Микропереключатель с рычагом без ролика (тип KW11-3Z / KW12-3), SPDT, использовать NC-контакт; упаковка 5 шт.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Основание</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ozon.ru/t/CrIV1po</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Только на M1 (в основании, без кольца). Служит нулём: кулачок на платформе нажимает в опорном положении; пределы поворота — программные. На M2…M4 концевиков нет — ограничение по углу AS5600 и току. COM → GND_L, NC → GPIO ESP32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обвязка концевика M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 кОм (подтяжка к 3,3 В) + 100 нФ (фильтр дребезга)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чат 16.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вход ESP32 — GPIO48 из резерва (предложение, «Аккуратно!» в распиновке); обработка по прерыванию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сетевой шнур адаптера (Schuko — IEC C13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REXANT 11-1121: вилка CEE 7/7 угловая — IEC 320 C13, 3×0,75 мм², 1,8 м (альтернатива: Power Cube 3×1,0 мм², 16 А)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.chipdip.ru/product/11-1121-shnur-setevoy-vilka-uglovaya-see-7-7-schuko-rexant-8518334503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вход адаптера GST220A — C14, шнур в комплект не входит; ток от сети ~1 А. Цена не заполнена; подойдёт любой имеющийся шнур от монитора/ПК</t>
+  </si>
+  <si>
     <t xml:space="preserve">Название модуля</t>
   </si>
   <si>
@@ -1215,6 +1284,9 @@
   </si>
   <si>
     <t xml:space="preserve">Списки используются проверкой данных на листе «Компоненты». Добавляя значение — дописывай сюда.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коды плат: MC — главная (контроллер), PS — питание, CH — канал привода (×4+1), LR — панель ЛР, GR — схват</t>
   </si>
 </sst>
 </file>
@@ -1594,8 +1666,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Components" displayName="Components" ref="A1:V55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:V55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Components" displayName="Components" ref="A1:V58" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:V58"/>
   <tableColumns count="22">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Узел"/>
@@ -1835,7 +1907,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V55"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -2367,7 +2439,7 @@
         <v>29</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="O8" s="4" t="s">
         <v>68</v>
@@ -2633,7 +2705,7 @@
         <v>85</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3" t="n">
@@ -2657,31 +2729,31 @@
         <v>33</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="n">
@@ -2719,28 +2791,28 @@
         <v>32</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>27</v>
@@ -2763,10 +2835,10 @@
         <v>85</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>966</v>
@@ -2783,37 +2855,37 @@
         <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="n">
@@ -2830,7 +2902,7 @@
         <v>85</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="n">
@@ -2851,28 +2923,28 @@
         <v>32</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>27</v>
@@ -2895,10 +2967,10 @@
         <v>85</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>518</v>
@@ -2918,28 +2990,28 @@
         <v>32</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>27</v>
@@ -2962,7 +3034,7 @@
         <v>85</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3" t="n">
@@ -2983,28 +3055,28 @@
         <v>32</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>27</v>
@@ -3030,7 +3102,7 @@
         <v>39</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>487</v>
@@ -3053,18 +3125,18 @@
         <v>33</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>37</v>
@@ -3094,7 +3166,7 @@
         <v>29</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="O19" s="4" t="s">
         <v>63</v>
@@ -3123,20 +3195,20 @@
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>27</v>
@@ -3159,10 +3231,10 @@
         <v>80</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>73</v>
@@ -3185,31 +3257,31 @@
         <v>33</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="n">
@@ -3226,7 +3298,7 @@
         <v>80</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="n">
@@ -3247,37 +3319,37 @@
         <v>32</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>1</v>
@@ -3293,10 +3365,10 @@
         <v>29</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0</v>
@@ -3316,39 +3388,39 @@
         <v>32</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>1</v>
@@ -3364,7 +3436,7 @@
         <v>29</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="n">
@@ -3385,28 +3457,28 @@
         <v>32</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>27</v>
@@ -3429,7 +3501,7 @@
         <v>80</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3" t="n">
@@ -3450,28 +3522,28 @@
         <v>32</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>27</v>
@@ -3494,7 +3566,7 @@
         <v>85</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3" t="n">
@@ -3515,34 +3587,34 @@
         <v>32</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="n">
@@ -3559,7 +3631,7 @@
         <v>29</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3" t="n">
@@ -3580,26 +3652,26 @@
         <v>32</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>27</v>
@@ -3622,10 +3694,10 @@
         <v>80</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>73</v>
@@ -3645,21 +3717,21 @@
         <v>32</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>37</v>
@@ -3689,7 +3761,7 @@
         <v>85</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O28" s="4" t="s">
         <v>75</v>
@@ -3712,37 +3784,37 @@
         <v>32</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>1</v>
@@ -3758,10 +3830,10 @@
         <v>29</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>108</v>
@@ -3781,28 +3853,28 @@
         <v>32</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>27</v>
@@ -3825,10 +3897,10 @@
         <v>80</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>130</v>
@@ -3848,30 +3920,30 @@
         <v>32</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>27</v>
@@ -3894,7 +3966,7 @@
         <v>80</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3" t="n">
@@ -3915,37 +3987,37 @@
         <v>32</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>2</v>
@@ -3961,7 +4033,7 @@
         <v>85</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3" t="n">
@@ -3982,37 +4054,37 @@
         <v>32</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>1</v>
@@ -4028,7 +4100,7 @@
         <v>29</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="n">
@@ -4049,28 +4121,28 @@
         <v>32</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>27</v>
@@ -4093,7 +4165,7 @@
         <v>85</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3" t="n">
@@ -4114,30 +4186,30 @@
         <v>32</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>27</v>
@@ -4160,7 +4232,7 @@
         <v>85</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O35" s="3"/>
       <c r="P35" s="3" t="n">
@@ -4181,36 +4253,36 @@
         <v>32</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="n">
@@ -4227,7 +4299,7 @@
         <v>85</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3" t="n">
@@ -4248,28 +4320,28 @@
         <v>32</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>27</v>
@@ -4289,13 +4361,13 @@
         <v>16</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>51</v>
+        <v>141</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>51</v>
@@ -4315,21 +4387,21 @@
         <v>32</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>37</v>
@@ -4337,13 +4409,13 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>5</v>
@@ -4359,7 +4431,7 @@
         <v>85</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="n">
@@ -4377,37 +4449,37 @@
         <v>0</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="n">
@@ -4424,7 +4496,7 @@
         <v>85</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3" t="n">
@@ -4442,37 +4514,37 @@
         <v>0</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="n">
@@ -4489,7 +4561,7 @@
         <v>85</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="O40" s="3"/>
       <c r="P40" s="3" t="n">
@@ -4507,35 +4579,35 @@
         <v>0</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="n">
@@ -4552,7 +4624,7 @@
         <v>85</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="O41" s="3"/>
       <c r="P41" s="3" t="n">
@@ -4570,37 +4642,37 @@
         <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="n">
@@ -4617,7 +4689,7 @@
         <v>85</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3" t="n">
@@ -4635,34 +4707,34 @@
         <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>28</v>
@@ -4682,7 +4754,7 @@
         <v>85</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="O43" s="3"/>
       <c r="P43" s="3" t="n">
@@ -4700,24 +4772,24 @@
         <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>37</v>
@@ -4730,7 +4802,7 @@
         <v>27</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="n">
@@ -4747,7 +4819,7 @@
         <v>85</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>39</v>
+        <v>218</v>
       </c>
       <c r="O44" s="3"/>
       <c r="P44" s="3" t="n">
@@ -4768,37 +4840,37 @@
         <v>32</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>4</v>
@@ -4814,10 +4886,10 @@
         <v>80</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>150</v>
@@ -4837,21 +4909,21 @@
         <v>32</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>37</v>
@@ -4859,13 +4931,13 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>1</v>
@@ -4881,7 +4953,7 @@
         <v>30</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="O46" s="3"/>
       <c r="P46" s="3" t="n">
@@ -4902,37 +4974,37 @@
         <v>32</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>1</v>
@@ -4948,7 +5020,7 @@
         <v>29</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="O47" s="3"/>
       <c r="P47" s="3" t="n">
@@ -4969,32 +5041,32 @@
         <v>32</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="V47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="n">
@@ -5011,7 +5083,7 @@
         <v>85</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="O48" s="3"/>
       <c r="P48" s="3" t="n">
@@ -5032,21 +5104,21 @@
         <v>32</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>37</v>
@@ -5054,13 +5126,13 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J49" s="3" t="n">
         <v>1</v>
@@ -5097,28 +5169,28 @@
         <v>32</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="C50" s="3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>27</v>
@@ -5162,28 +5234,28 @@
         <v>32</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>27</v>
@@ -5227,28 +5299,28 @@
         <v>32</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>27</v>
@@ -5274,7 +5346,7 @@
         <v>51</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="P52" s="3" t="n">
         <v>0</v>
@@ -5297,29 +5369,31 @@
         <v>33</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
+      <c r="F53" s="3" t="s">
+        <v>284</v>
+      </c>
       <c r="G53" s="3" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="n">
@@ -5336,11 +5410,13 @@
         <v>29</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O53" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="P53" s="3" t="n">
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="Q53" s="3" t="n">
         <v>0</v>
@@ -5351,40 +5427,40 @@
       </c>
       <c r="S53" s="3" t="n">
         <f aca="false">R53*P53</f>
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="T53" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>92</v>
+        <v>286</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="n">
@@ -5422,31 +5498,31 @@
         <v>32</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>28</v>
@@ -5466,7 +5542,7 @@
         <v>85</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="n">
@@ -5490,7 +5566,206 @@
         <v>33</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>288</v>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <f aca="false">J56*K56</f>
+        <v>1</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <f aca="false">IF(D56="Внутри модуля",0,MAX(0,L56-Q56))</f>
+        <v>1</v>
+      </c>
+      <c r="S56" s="3" t="n">
+        <f aca="false">R56*P56</f>
+        <v>26</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U56" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="V56" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <f aca="false">J57*K57</f>
+        <v>2</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <f aca="false">IF(D57="Внутри модуля",0,MAX(0,L57-Q57))</f>
+        <v>2</v>
+      </c>
+      <c r="S57" s="3" t="n">
+        <f aca="false">R57*P57</f>
+        <v>0</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <f aca="false">J58*K58</f>
+        <v>1</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <f aca="false">IF(D58="Внутри модуля",0,MAX(0,L58-Q58))</f>
+        <v>1</v>
+      </c>
+      <c r="S58" s="3" t="n">
+        <f aca="false">R58*P58</f>
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -5532,7 +5807,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Значение должно быть из списка на листе «Справочники»" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N2:N500" type="list">
-      <formula1>Справочники!$F$2:$F$7</formula1>
+      <formula1>Справочники!$F$2:$F$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Значение должно быть из списка на листе «Справочники»" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="T2:T500" type="list">
@@ -5598,28 +5873,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>14</v>
@@ -5630,7 +5905,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>23</v>
@@ -5639,10 +5914,10 @@
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="G2" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A2,Компоненты!$A:$A,0)),"")</f>
@@ -5665,7 +5940,7 @@
         <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>23</v>
@@ -5674,10 +5949,10 @@
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="G3" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A3,Компоненты!$A:$A,0)),"")</f>
@@ -5697,22 +5972,22 @@
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="G4" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A4,Компоненты!$A:$A,0)),"")</f>
@@ -5727,27 +6002,27 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="G5" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A5,Компоненты!$A:$A,0)),"")</f>
@@ -5762,27 +6037,27 @@
         <v>0</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="G6" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A6,Компоненты!$A:$A,0)),"")</f>
@@ -5797,27 +6072,27 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="G7" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A7,Компоненты!$A:$A,0)),"")</f>
@@ -5832,27 +6107,27 @@
         <v>0</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="G8" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A8,Компоненты!$A:$A,0)),"")</f>
@@ -5870,22 +6145,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="G9" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A9,Компоненты!$A:$A,0)),"")</f>
@@ -5900,12 +6175,12 @@
         <v>4</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -5955,316 +6230,316 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>350</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -6297,7 +6572,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6305,13 +6580,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>18</v>
@@ -6323,36 +6598,36 @@
       </c>
       <c r="B4" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$H:$H,A4)</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C4" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$H:$H,A4)</f>
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D4" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$R:$R,Компоненты!$H:$H,A4)</f>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E4" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$H:$H,A4)</f>
-        <v>8807</v>
+        <v>9623</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$H:$H,A5)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$H:$H,A5)</f>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$R:$R,Компоненты!$H:$H,A5)</f>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E5" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$H:$H,A5)</f>
@@ -6361,19 +6636,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$H:$H,A6)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$H:$H,A6)</f>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$R:$R,Компоненты!$H:$H,A6)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$H:$H,A6)</f>
@@ -6382,23 +6657,23 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">SUM(B4:B6)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">SUM(C4:C6)</f>
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D7" s="11" t="n">
         <f aca="false">SUM(D4:D6)</f>
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">SUM(E4:E6)</f>
-        <v>9839</v>
+        <v>10655</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6406,13 +6681,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>18</v>
@@ -6424,24 +6699,24 @@
       </c>
       <c r="B11" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A11)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A11)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A11,Компоненты!$H:$H,"Уточняется")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$B:$B,A11)</f>
-        <v>6724</v>
+        <v>7514</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B12" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A12)</f>
@@ -6462,15 +6737,15 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B13" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A13)</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A13)</f>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A13,Компоненты!$H:$H,"Уточняется")</f>
@@ -6478,12 +6753,12 @@
       </c>
       <c r="E13" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$B:$B,A13)</f>
-        <v>1060</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B14" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A14)</f>
@@ -6504,7 +6779,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B15" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A15)</f>
@@ -6525,7 +6800,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B16" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A16)</f>
@@ -6546,7 +6821,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B17" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A17)</f>
@@ -6567,7 +6842,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B18" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A18)</f>
@@ -6588,23 +6863,23 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">SUM(B11:B18)</f>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C19" s="11" t="n">
         <f aca="false">SUM(C11:C18)</f>
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D19" s="11" t="n">
         <f aca="false">SUM(D11:D18)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" s="11" t="n">
         <f aca="false">SUM(E11:E18)</f>
-        <v>9839</v>
+        <v>10655</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6612,7 +6887,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6621,12 +6896,12 @@
       </c>
       <c r="B23" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$G:$G,A23)</f>
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B24" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$G:$G,A24)</f>
@@ -6635,11 +6910,11 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B25" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$G:$G,A25)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6647,10 +6922,10 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6672,16 +6947,16 @@
       </c>
       <c r="B29" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$D:$D,A29)</f>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C29" s="10" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$D:$D,A29)</f>
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B30" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$D:$D,A30)</f>
@@ -6694,7 +6969,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="B32" s="10" t="n">
         <f aca="false">COUNTIFS(Компоненты!$T:$T,"Да")</f>
@@ -6703,7 +6978,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
       <c r="B33" s="10" t="n">
         <f aca="false">COUNTA(Отклонено!$A:$A)-1</f>
@@ -6712,7 +6987,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -6731,7 +7006,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="1" style="1" width="18"/>
@@ -6745,10 +7020,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>12</v>
@@ -6757,7 +7032,7 @@
         <v>13</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6777,30 +7052,30 @@
         <v>29</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>37</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>85</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>32</v>
@@ -6808,64 +7083,88 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>80</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>30</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>241</v>
+        <v>244</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>261</v>
+        <v>265</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F10" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F11" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>396</v>
+        <v>419</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F14" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
   </sheetData>

--- a/bom/Component_Base.xlsx
+++ b/bom/Component_Base.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="451">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">https://ozon.ru/t/zLw6TpD</t>
   </si>
   <si>
-    <t xml:space="preserve">Через контакт — только ток катушки реле; индикатор запитать с выхода реле (горит, когда +24 подан). Прежний — тумблер REXANT 15 А (ozon.ru/t/j7BR2sW), судьба уточняется</t>
+    <t xml:space="preserve">Через контакт — только ток катушки реле (замыкает A2 на GND_P); подсветка 24 В с выхода реле (горит, когда +24 подан). Разъём на PS — XP1 4-конт. (E-092): контакт 1–2, подсветка 3–4. Прежний — тумблер REXANT 15 А (ozon.ru/t/j7BR2sW), судьба уточняется</t>
   </si>
   <si>
     <t xml:space="preserve">E-003</t>
@@ -188,10 +188,28 @@
     <t xml:space="preserve">Параллельно шине +24 после предохранителя; ограничение ниже пределов XL4015E (38 В) и DRV8871 (45 В). SMBJ28A с доски отклонён (R-015)</t>
   </si>
   <si>
-    <t xml:space="preserve">E-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Индикатор «+24 есть»</t>
+    <t xml:space="preserve">E-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC-DC 24 → 5P (силовые 5 В)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XL4015E, 5 А, регулируемый</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ozon.ru/t/v0TomWG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лист питания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выставить 5,0 В и зафиксировать; питает ТОЛЬКО +5P: катушки NRP-02 ×16 (~640 мА), оптореле, выходы 6N137. Остров — от E-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Индикатор «+5P есть»</t>
   </si>
   <si>
     <t xml:space="preserve">Светодиод 2 В (жёлтый по реестру)</t>
@@ -200,16 +218,169 @@
     <t xml:space="preserve">https://ozon.ru/t/1fZdgL1</t>
   </si>
   <si>
-    <t xml:space="preserve">лист питания</t>
-  </si>
-  <si>
     <t xml:space="preserve">Цвет не фиксирован</t>
   </si>
   <si>
-    <t xml:space="preserve">E-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Резистор индикатора +24</t>
+    <t xml:space="preserve">E-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резистор индикатора +5P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 Ом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ozon.ru/t/QWYR5Dy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈20 мА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Изолированный DC-DC 24 → 5 (логический остров)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornsun VRB2405YMD-10WR3 (24 → 5 В, 10 Вт / 2 А, стабилизированный, изоляция 1,5 кВ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Граница</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Питается от шины +24 (не от XL4015E). Остров ≈0,4 А + линия схвата до 1 А (E-083). Выводы по datasheet Mornsun 2026.03 (YMD, 25,4 × 25,4): 1 Ctrl (свободен), 2 GND, 3 Vin, 4 +Vo, 5 нет вывода, 6 0V; вывод ⌀1,0, отверстие 1,5. B0505S-1W из реестра не используется (R-013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Источник 3,3 В логики</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пин 3V3 платы YD-ESP32-S3 (бортовой LDO 5→3,3 В, 1 А)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Логическая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отдельного компонента нет. Потребители: TCA9548A, подтяжки I2C/RST, подтяжка выхода оптрона KH (&lt;20 мА)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дроссель фильтра +5P (L1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talema DPO-3.0-22 — тороид 22 мкГн, 3 А, 50 мОм, ⌀14 × 8 мм, выводы 0,5 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.chipdip.ru/product/dpo-3-0-22-drossel-pomehopodavlyayuschiy-dpu-22mkgn-talema-8002552890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чат 17.09 (утверждено Mikhail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LC-фильтр пульсаций после модуля XL4015E вне его петли ОС: L1 + C1 (E-093) + C2 (E-094), f₀ ≈ 1,6 кГц; падение ≈ 50 мВ/А. Footprint L_Toroid_D20_P10.16mm. Цена не заполнена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Контроллер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Микроконтроллер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YD-ESP32-S3 N16R8 DevKit (ESP32-S3-DevKitC-1 clone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ozon.ru/t/Wcg9F9p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Да</t>
+  </si>
+  <si>
+    <t xml:space="preserve">доска + чат 15.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Распиновка принята («Аккуратно!»); ПК — родной USB GPIO19/20, запас CH343 GPIO43/44; VIN от изолированных +5; GPIO48 — концевик M1 (предложение)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтяжки главной шины I2C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,7 кОм на 3,3 В</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Предложение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чат 15.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На модуле ESP32 подтяжек нет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I2C/датчики</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мультиплексор I2C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CJMCU-9548 (TCA9548A/PCA9548A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ozon.ru/t/QWYQvBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VCC 3,3 В; A2 GND; A0/A1 от ESP32 (GPIO47/38); каналы 0–3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтяжка RST мультиплексора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 кОм на 3,3 В</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ линия на GPIO42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Режим ЛР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кнопка переключения режима KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EKF S-Pro67, 19 мм, с фиксатором, белая подсветка 24 В</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ozon.ru/t/3QXN2ZT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Контакт коммутирует +5P на шину KH; подсветка от +24 с PS (XP5, E-018) кабелем напрямую к кнопке, минуя плату LR. Уточнить группу контактов (нужен 1×NO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтяжка шины KH на землю</t>
   </si>
   <si>
     <t xml:space="preserve">1 кОм</t>
@@ -218,396 +389,216 @@
     <t xml:space="preserve">https://ozon.ru/t/gmtx6pg</t>
   </si>
   <si>
-    <t xml:space="preserve">≈22 мА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC-DC 24 → 5P (силовые 5 В)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XL4015E, 5 А, регулируемый</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ozon.ru/t/v0TomWG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Выставить 5,0 В и зафиксировать; питает ТОЛЬКО +5P: катушки NRP-02 ×16 (~640 мА), оптореле, выходы 6N137. Остров — от E-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Индикатор «+5P есть»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Резистор индикатора +5P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150 Ом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ozon.ru/t/QWYR5Dy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≈20 мА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Изолированный DC-DC 24 → 5 (логический остров)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornsun VRB2405YMD-10WR3 (24 → 5 В, 10 Вт / 2 А, стабилизированный, изоляция 1,5 кВ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Граница</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Питается от шины +24 (не от XL4015E). Остров ≈0,4 А + линия схвата до 1 А (E-083). B0505S-1W из реестра не используется (R-013)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Источник 3,3 В логики</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пин 3V3 платы YD-ESP32-S3 (бортовой LDO 5→3,3 В, 1 А)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Логическая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отдельного компонента нет. Потребители: TCA9548A, подтяжки I2C/RST, подтяжка выхода оптрона KH (&lt;20 мА)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Фильтр шины +5P после XL4015E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LC/RC (дроссель + 470 мкФ + керамика)</t>
+    <t xml:space="preserve">E-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оптореле сигнала KH → ESP32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КР293КП2Б (из запаса: в реестре 12 шт., на RELE нужно 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ozon.ru/t/sXzB21l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Статический сигнал — скорость не важна; выход замыкает GPIO41 на GND_L; вход инвертный (в ПО). PC817 отклонён (R-014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резисторы оптореле KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470 Ом (LED, от шины KH 5 В, ~8 мА) + 10 кОм (подтяжка GPIO41 к 3,3 В)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Номиналы — предложение под КР293КП2Б (LED ≤10 мА)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Канал привода</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Драйвер ДПТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRV8871 (модуль, клон Adafruit), 6,5–45 В</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кандидат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уточняется</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ozon.ru/t/tPvFr4r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">доска</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ждёт мотора: до 3,6 А пик / ~2 А длит. Посадочное место сделать разъёмным</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Микросхема драйвера на модуле</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Внутри модуля</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRV8871DDAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">модуль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Приходит с модулем E-030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Изолятор PWM IN1/IN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6N137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чат 14.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Замена КР293КП2Б на PWM 20 кГц; выход инвертирующий (в ПО)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резистор LED 6N137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220 Ом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Общий для ESP32 (3,3 В) и студента (3,3/5 В)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтяжка выхода 6N137 к +5P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,7 кОм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оптореле сигнала RELE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КР293КП2Б</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В реестре 12 шт. → нужно 4 (упаковка по 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Резистор LED оптореле</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≤10 мА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Реле аварийного отключения питания ДПТ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HF49FD/005-1H11 (Hongfa, 5 В, 5 А, 30 В DC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ozon.ru/t/ukwD77G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Годится только при стопорном токе мотора ≤ 5 А; катушка 24 мА через КР293КП2Б</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Датчик тока</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACS712-20A (модуль), 100 мВ/А</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ozon.ru/t/1fZ9B9H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">доска + чат 14.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сигнальная часть — логические +5; измеряемая цепь — силовая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Микросхема датчика тока на модуле</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACS712ELCTR-20A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Приходит с модулем E-038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согласование выхода ACS712 с ADC ESP32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Делитель 10 кОм + 20 кОм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0–5 В → 0–3,3 В; не утверждено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Двигатель ДПТ 24 В</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(кандидат FGA-43246000-G149 отложен)</t>
   </si>
   <si>
     <t xml:space="preserve">Только функция</t>
   </si>
   <si>
-    <t xml:space="preserve">Предложение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">чат 15.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пульсации XL4015E под нагрузкой</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Контроллер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Микроконтроллер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YD-ESP32-S3 N16R8 DevKit (ESP32-S3-DevKitC-1 clone)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ozon.ru/t/Wcg9F9p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Да</t>
-  </si>
-  <si>
-    <t xml:space="preserve">доска + чат 15.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Распиновка принята («Аккуратно!»); ПК — родной USB GPIO19/20, запас CH343 GPIO43/44; VIN от изолированных +5; GPIO48 — концевик M1 (предложение)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подтяжки главной шины I2C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,7 кОм на 3,3 В</t>
-  </si>
-  <si>
-    <t xml:space="preserve">На модуле ESP32 подтяжек нет</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2C/датчики</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мультиплексор I2C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CJMCU-9548 (TCA9548A/PCA9548A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ozon.ru/t/QWYQvBC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VCC 3,3 В; A2 GND; A0/A1 от ESP32 (GPIO47/38); каналы 0–3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подтяжка RST мультиплексора</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 кОм на 3,3 В</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ линия на GPIO42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Режим ЛР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кнопка переключения режима KH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EKF S-Pro67, 19 мм, с фиксатором, белая подсветка 24 В</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ozon.ru/t/3QXN2ZT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Контакт коммутирует +5P на шину KH; подсветка от +24. Уточнить группу контактов (нужен 1×NO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подтяжка шины KH на землю</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оптореле сигнала KH → ESP32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КР293КП2Б (из запаса: в реестре 12 шт., на RELE нужно 4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ozon.ru/t/sXzB21l</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Статический сигнал — скорость не важна; выход замыкает GPIO41 на GND_L; вход инвертный (в ПО). PC817 отклонён (R-014)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Резисторы оптореле KH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470 Ом (LED, от шины KH 5 В, ~8 мА) + 10 кОм (подтяжка GPIO41 к 3,3 В)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Номиналы — предложение под КР293КП2Б (LED ≤10 мА)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Канал привода</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Драйвер ДПТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRV8871 (модуль, клон Adafruit), 6,5–45 В</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кандидат</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Уточняется</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ozon.ru/t/tPvFr4r</t>
-  </si>
-  <si>
-    <t xml:space="preserve">доска</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ждёт мотора: до 3,6 А пик / ~2 А длит. Посадочное место сделать разъёмным</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Микросхема драйвера на модуле</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Внутри модуля</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRV8871DDAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">модуль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Приходит с модулем E-030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Изолятор PWM IN1/IN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6N137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">чат 14.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Замена КР293КП2Б на PWM 20 кГц; выход инвертирующий (в ПО)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Резистор LED 6N137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220 Ом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Общий для ESP32 (3,3 В) и студента (3,3/5 В)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подтяжка выхода 6N137 к +5P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,7 кОм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оптореле сигнала RELE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КР293КП2Б</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В реестре 12 шт. → нужно 4 (упаковка по 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Резистор LED оптореле</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≤10 мА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Реле аварийного отключения питания ДПТ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HF49FD/005-1H11 (Hongfa, 5 В, 5 А, 30 В DC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ozon.ru/t/ukwD77G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Годится только при стопорном токе мотора ≤ 5 А; катушка 24 мА через КР293КП2Б</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Датчик тока</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACS712-20A (модуль), 100 мВ/А</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ozon.ru/t/1fZ9B9H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">доска + чат 14.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сигнальная часть — логические +5; измеряемая цепь — силовая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Микросхема датчика тока на модуле</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACS712ELCTR-20A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Приходит с модулем E-038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Согласование выхода ACS712 с ADC ESP32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Делитель 10 кОм + 20 кОм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0–5 В → 0–3,3 В; не утверждено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Двигатель ДПТ 24 В</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(кандидат FGA-43246000-G149 отложен)</t>
-  </si>
-  <si>
     <t xml:space="preserve">(8)</t>
   </si>
   <si>
@@ -863,13 +854,13 @@
     <t xml:space="preserve">Реле шины 24 В (включение питания стенда)</t>
   </si>
   <si>
-    <t xml:space="preserve">NRP-15-C-24D, катушка 24 В DC, контакт 30 А, SPDT</t>
+    <t xml:space="preserve">NRP-15-C-24D (NCR), катушка 24 В DC 619 Ом / 39 мА / 0,93 Вт, контакт 1C: 20 А 28 В DC (30 А — только 1A)</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.chipdip.ru/product/nrp-15-c-24d</t>
   </si>
   <si>
-    <t xml:space="preserve">Контакт рвёт шину +24 после предохранителя; катушка через кнопку E-002 от +24 до реле. Проверить в даташите ток контакта для DC (ожидаемо 15–20 А при 24 В). Цена не заполнена</t>
+    <t xml:space="preserve">Контакт COM–NO рвёт шину +24 после предохранителя; A1 — +24V_IN постоянно, A2 — на GND_P через контакт кнопки E-002 (XP1). NC не используется. По datasheet NCR NRP15 (ncr.hk): 1C — 20 А/28 В DC. Footprint Relay_NRP-15_1C — вид снизу datasheet зеркалирован, перед пайкой прозвонить COM–NC обесточенного реле</t>
   </si>
   <si>
     <t xml:space="preserve">E-014</t>
@@ -962,6 +953,90 @@
     <t xml:space="preserve">Вход адаптера GST220A — C14, шнур в комплект не входит; ток от сети ~1 А. Цена не заполнена; подойдёт любой имеющийся шнур от монитора/ПК</t>
   </si>
   <si>
+    <t xml:space="preserve">E-017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Клеммник силовых линий 24 В на плате PS (вход J1, выходы J3…J7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG301-5.0-02P-12 (KLS2-301-5.00-02P-2S), Degson — клеммник винтовой на плату, 2 контакта, шаг 5,0 мм, прямой, 15 А / 300 В (UL), провод 0,75–1,5 мм² (22–14 AWG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.chipdip.ru/product/dg301-5.0-02p-12-kls2-301-5.00-02p-2s-klemmnik-degson-9000110359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XT1 (вход, 18 AWG), XT2…XT6 (выходы +24, 20–22 AWG). По чертежу Degson 200102539: корпус 5,0×N × 7,6 × 10 мм, вывод ⌀1,0, отверстие 1,2 (в footprint 1,3), винт M2.5, момент 0,29 Н·м. Ответная часть не нужна; полярность — шёлкографией; стыкуются в ряд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разъём сигнальный малого тока на PS (LED панели XP4, питание подсветки KH XP5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JST B2B-XH-A (LF)(SN) — вилка прямая на плату, серия XH, 2,5 мм, 2 контакта, 3 А</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.chipdip.ru/product/b2b-xh-a-lf-sn-razem-shtyrevoy-na-platu-2.5-mm-2-jst-9000015961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XP4 (LED «+5P есть» E-008), XP5 (+24 на подсветку кнопки KH E-024, кабель к кнопке). Ответная часть на кабель: корпус XHP-2 + контакты SXH-001T-P0.6 ×2 — докупить к каждому разъёму. Тот же тип — на LR и MC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разъём питания логики PS → MC (+5P XP2, +5 остров XP3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JST B2P-VH — вилка прямая на плату, серия VH, 3,96 мм, 2 контакта, 10 А</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.chipdip.ru/product/b2p-vh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XP2 (+5P → MC), XP3 (+5 остров → MC, с выхода U2). Ответная часть на кабель: корпус VHR-2N + контакты SVH-21T-P1.1 ×2 (18–22 AWG) — докупить к каждому разъёму</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разъём кнопки питания на PS (XP1: контакт катушки + подсветка)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JST B4B-XH-A (LF)(SN) — вилка прямая на плату, серия XH, 2,5 мм, 4 контакта, 3 А</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.chipdip.ru/product/b4b-xh-a-lf-sn-razem-shtyrevoy-4-kontakta-2.5mm-na-jst-9000628021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XP1: 1 — катушка K1 (A2), 2 — GND_P (контакт кнопки замыкает 1–2), 3 — подсветка GND_P, 4 — подсветка +24V после реле. Ответная часть на кабель: корпус XHP-4 + контакты SXH-001T-P0.6 ×4 — докупить. Цена не заполнена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Конденсатор фильтра +5P (C1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Электролитический 470 мкФ 16 В, 105 °C, low ESR, ⌀8 мм, шаг 3,5 мм (любой производитель)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footprint CP_Radial_D8.0mm_P3.50mm; «+» — вывод 1. Конкретную марку выбрать при закупке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Конденсатор фильтра +5P (C2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Керамический 0,1 мкФ 50 В X7R, выводной, шаг 5 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footprint C_Disc_P5.00mm. Конкретную марку выбрать при закупке</t>
+  </si>
+  <si>
     <t xml:space="preserve">Название модуля</t>
   </si>
   <si>
@@ -1248,6 +1323,21 @@
   </si>
   <si>
     <t xml:space="preserve">Ограничение SMBJ28A (~45 В) выше предела XL4015E (38 В); SMCJ26A мощнее и ограничивает ниже</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отдельный индикатор «+24 есть» на панели: светодиод E-005 + резистор 1 кОм E-006 (R1, XP4 на PS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Встроенная подсветка 24 В кнопки питания E-002 через 4-конт. разъём XP1 (E-092), питание с выхода реле</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кнопка уже содержит индикатор 24 В; отдельный светодиод и резистор дублируют его</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.09.2026</t>
   </si>
   <si>
     <t xml:space="preserve">Сводка по базе компонентов (формулы по листу «Компоненты»)</t>
@@ -1296,7 +1386,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1336,6 +1426,13 @@
       <u val="single"/>
       <sz val="10"/>
       <color rgb="FF0563C1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1429,7 +1526,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1451,6 +1548,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1458,11 +1559,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1478,11 +1579,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1495,7 +1596,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1531,6 +1632,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF7F7F7F"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1666,8 +1775,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Components" displayName="Components" ref="A1:V58" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:V58"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Components" displayName="Components" ref="A1:V61" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:V61"/>
   <tableColumns count="22">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Узел"/>
@@ -1907,7 +2016,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V58"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -2278,7 +2387,7 @@
         <v>55</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
@@ -2305,13 +2414,13 @@
         <v>29</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="O6" s="4" t="s">
         <v>57</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>68</v>
+        <v>189</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>0</v>
@@ -2322,7 +2431,7 @@
       </c>
       <c r="S6" s="3" t="n">
         <f aca="false">R6*P6</f>
-        <v>68</v>
+        <v>189</v>
       </c>
       <c r="T6" s="3" t="s">
         <v>32</v>
@@ -2372,13 +2481,13 @@
         <v>29</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="O7" s="4" t="s">
         <v>63</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>0</v>
@@ -2389,7 +2498,7 @@
       </c>
       <c r="S7" s="3" t="n">
         <f aca="false">R7*P7</f>
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="T7" s="3" t="s">
         <v>32</v>
@@ -2412,7 +2521,7 @@
         <v>66</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
@@ -2445,7 +2554,7 @@
         <v>68</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>189</v>
+        <v>84</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>0</v>
@@ -2456,7 +2565,7 @@
       </c>
       <c r="S8" s="3" t="n">
         <f aca="false">R8*P8</f>
-        <v>189</v>
+        <v>84</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>32</v>
@@ -2483,7 +2592,7 @@
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>27</v>
@@ -2503,16 +2612,14 @@
         <v>1</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="O9" s="4"/>
       <c r="P9" s="3" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>0</v>
@@ -2523,34 +2630,34 @@
       </c>
       <c r="S9" s="3" t="n">
         <f aca="false">R9*P9</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>27</v>
@@ -2570,16 +2677,14 @@
         <v>1</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>75</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="O10" s="3"/>
       <c r="P10" s="3" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0</v>
@@ -2590,34 +2695,34 @@
       </c>
       <c r="S10" s="3" t="n">
         <f aca="false">R10*P10</f>
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>27</v>
@@ -2637,12 +2742,14 @@
         <v>1</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="N11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="O11" s="4"/>
+      <c r="O11" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="P11" s="3" t="n">
         <v>0</v>
       </c>
@@ -2661,28 +2768,28 @@
         <v>32</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>27</v>
@@ -2702,75 +2809,77 @@
         <v>1</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="O12" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>91</v>
+      </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>966</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="3" t="n">
         <f aca="false">IF(D12="Внутри модуля",0,MAX(0,L12-Q12))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="3" t="n">
         <f aca="false">R12*P12</f>
         <v>0</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="C13" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="3" t="n">
         <f aca="false">J13*K13</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="O13" s="3"/>
       <c r="P13" s="3" t="n">
@@ -2781,7 +2890,7 @@
       </c>
       <c r="R13" s="3" t="n">
         <f aca="false">IF(D13="Внутри модуля",0,MAX(0,L13-Q13))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" s="3" t="n">
         <f aca="false">R13*P13</f>
@@ -2791,28 +2900,28 @@
         <v>32</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>27</v>
@@ -2832,16 +2941,16 @@
         <v>1</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>966</v>
+        <v>518</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>1</v>
@@ -2855,54 +2964,54 @@
         <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="3" t="n">
         <f aca="false">J15*K15</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="n">
@@ -2913,7 +3022,7 @@
       </c>
       <c r="R15" s="3" t="n">
         <f aca="false">IF(D15="Внутри модуля",0,MAX(0,L15-Q15))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" s="3" t="n">
         <f aca="false">R15*P15</f>
@@ -2923,28 +3032,28 @@
         <v>32</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>27</v>
@@ -2964,54 +3073,54 @@
         <v>1</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>518</v>
+        <v>487</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="3" t="n">
         <f aca="false">IF(D16="Внутри модуля",0,MAX(0,L16-Q16))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="3" t="n">
         <f aca="false">R16*P16</f>
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="T16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>27</v>
@@ -3031,14 +3140,16 @@
         <v>1</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="O17" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="P17" s="3" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>0</v>
@@ -3049,34 +3160,32 @@
       </c>
       <c r="S17" s="3" t="n">
         <f aca="false">R17*P17</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>116</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="V17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>27</v>
@@ -3096,16 +3205,16 @@
         <v>1</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>121</v>
+        <v>79</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>487</v>
+        <v>73</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>0</v>
@@ -3116,7 +3225,7 @@
       </c>
       <c r="S18" s="3" t="n">
         <f aca="false">R18*P18</f>
-        <v>487</v>
+        <v>73</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>32</v>
@@ -3125,180 +3234,186 @@
         <v>33</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L19" s="3" t="n">
         <f aca="false">J19*K19</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="O19" s="4" t="s">
-        <v>63</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="O19" s="3"/>
       <c r="P19" s="3" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="3" t="n">
         <f aca="false">IF(D19="Внутри модуля",0,MAX(0,L19-Q19))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" s="3" t="n">
         <f aca="false">R19*P19</f>
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="T19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="V19" s="3"/>
+        <v>99</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="3"/>
+        <v>135</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="J20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20" s="3" t="n">
         <f aca="false">J20*K20</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" s="3" t="n">
         <f aca="false">IF(D20="Внутри модуля",0,MAX(0,L20-Q20))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="n">
         <f aca="false">R20*P20</f>
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>33</v>
+        <v>139</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" s="3"/>
       <c r="F21" s="3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I21" s="3"/>
+        <v>135</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>136</v>
+      </c>
       <c r="J21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L21" s="3" t="n">
         <f aca="false">J21*K21</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="n">
@@ -3309,7 +3424,7 @@
       </c>
       <c r="R21" s="3" t="n">
         <f aca="false">IF(D21="Внутри модуля",0,MAX(0,L21-Q21))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S21" s="3" t="n">
         <f aca="false">R21*P21</f>
@@ -3319,66 +3434,62 @@
         <v>32</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>140</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I22" s="3"/>
       <c r="J22" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L22" s="3" t="n">
         <f aca="false">J22*K22</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>142</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O22" s="3"/>
       <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="n">
         <f aca="false">IF(D22="Внутри модуля",0,MAX(0,L22-Q22))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S22" s="3" t="n">
         <f aca="false">R22*P22</f>
@@ -3388,55 +3499,51 @@
         <v>32</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>134</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="E23" s="3"/>
       <c r="F23" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>140</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I23" s="3"/>
       <c r="J23" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L23" s="3" t="n">
         <f aca="false">J23*K23</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3" t="n">
@@ -3447,7 +3554,7 @@
       </c>
       <c r="R23" s="3" t="n">
         <f aca="false">IF(D23="Внутри модуля",0,MAX(0,L23-Q23))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">R23*P23</f>
@@ -3457,34 +3564,34 @@
         <v>32</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="n">
@@ -3498,10 +3605,10 @@
         <v>8</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O24" s="3"/>
       <c r="P24" s="3" t="n">
@@ -3522,28 +3629,26 @@
         <v>32</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>155</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="V24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>27</v>
@@ -3553,133 +3658,141 @@
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L25" s="3" t="n">
         <f aca="false">J25*K25</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="O25" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="P25" s="3" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
         <f aca="false">IF(D25="Внутри модуля",0,MAX(0,L25-Q25))</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S25" s="3" t="n">
         <f aca="false">R25*P25</f>
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="T25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3" t="s">
-        <v>162</v>
+        <v>67</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L26" s="3" t="n">
         <f aca="false">J26*K26</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="O26" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="P26" s="3" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R26" s="3" t="n">
         <f aca="false">IF(D26="Внутри модуля",0,MAX(0,L26-Q26))</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S26" s="3" t="n">
         <f aca="false">R26*P26</f>
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="V26" s="3"/>
+        <v>139</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I27" s="3"/>
+        <v>135</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>169</v>
+      </c>
       <c r="J27" s="3" t="n">
         <v>1</v>
       </c>
@@ -3691,16 +3804,16 @@
         <v>4</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="N27" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>0</v>
@@ -3711,34 +3824,34 @@
       </c>
       <c r="S27" s="3" t="n">
         <f aca="false">R27*P27</f>
-        <v>292</v>
+        <v>432</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3" t="s">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>27</v>
@@ -3758,64 +3871,64 @@
         <v>4</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>75</v>
+        <v>175</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R28" s="3" t="n">
         <f aca="false">IF(D28="Внутри модуля",0,MAX(0,L28-Q28))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
         <f aca="false">R28*P28</f>
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="T28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>172</v>
+      </c>
       <c r="F29" s="3" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>173</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I29" s="3"/>
       <c r="J29" s="3" t="n">
         <v>1</v>
       </c>
@@ -3827,90 +3940,88 @@
         <v>4</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="N29" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>174</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O29" s="3"/>
       <c r="P29" s="3" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R29" s="3" t="n">
         <f aca="false">IF(D29="Внутри модуля",0,MAX(0,L29-Q29))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="n">
         <f aca="false">R29*P29</f>
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I30" s="3"/>
+        <v>98</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="J30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L30" s="3" t="n">
         <f aca="false">J30*K30</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="O30" s="4" t="s">
-        <v>179</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O30" s="3"/>
       <c r="P30" s="3" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R30" s="3" t="n">
         <f aca="false">IF(D30="Внутри модуля",0,MAX(0,L30-Q30))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S30" s="3" t="n">
         <f aca="false">R30*P30</f>
@@ -3920,38 +4031,38 @@
         <v>32</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I31" s="3"/>
+      <c r="I31" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="J31" s="3" t="n">
         <v>1</v>
       </c>
@@ -3963,10 +4074,10 @@
         <v>4</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="N31" s="3" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="O31" s="3"/>
       <c r="P31" s="3" t="n">
@@ -3977,7 +4088,7 @@
       </c>
       <c r="R31" s="3" t="n">
         <f aca="false">IF(D31="Внутри модуля",0,MAX(0,L31-Q31))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S31" s="3" t="n">
         <f aca="false">R31*P31</f>
@@ -3987,64 +4098,62 @@
         <v>32</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>189</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I32" s="3"/>
       <c r="J32" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L32" s="3" t="n">
         <f aca="false">J32*K32</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R32" s="3" t="n">
         <f aca="false">IF(D32="Внутри модуля",0,MAX(0,L32-Q32))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="n">
         <f aca="false">R32*P32</f>
@@ -4054,38 +4163,38 @@
         <v>32</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E33" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="F33" s="3" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>194</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I33" s="3"/>
       <c r="J33" s="3" t="n">
         <v>1</v>
       </c>
@@ -4097,10 +4206,10 @@
         <v>4</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="N33" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="n">
@@ -4111,7 +4220,7 @@
       </c>
       <c r="R33" s="3" t="n">
         <f aca="false">IF(D33="Внутри модуля",0,MAX(0,L33-Q33))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S33" s="3" t="n">
         <f aca="false">R33*P33</f>
@@ -4121,58 +4230,60 @@
         <v>32</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="F34" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L34" s="3" t="n">
         <f aca="false">J34*K34</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R34" s="3" t="n">
         <f aca="false">IF(D34="Внутри модуля",0,MAX(0,L34-Q34))</f>
@@ -4186,30 +4297,28 @@
         <v>32</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>197</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="E35" s="3"/>
       <c r="F35" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>27</v>
@@ -4219,87 +4328,87 @@
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L35" s="3" t="n">
         <f aca="false">J35*K35</f>
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="O35" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
         <f aca="false">IF(D35="Внутри модуля",0,MAX(0,L35-Q35))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S35" s="3" t="n">
         <f aca="false">R35*P35</f>
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>207</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I36" s="3"/>
+        <v>135</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="J36" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L36" s="3" t="n">
         <f aca="false">J36*K36</f>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3" t="n">
@@ -4310,128 +4419,126 @@
       </c>
       <c r="R36" s="3" t="n">
         <f aca="false">IF(D36="Внутри модуля",0,MAX(0,L36-Q36))</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S36" s="3" t="n">
         <f aca="false">R36*P36</f>
         <v>0</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L37" s="3" t="n">
         <f aca="false">J37*K37</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="O37" s="4" t="s">
-        <v>212</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="O37" s="3"/>
       <c r="P37" s="3" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R37" s="3" t="n">
         <f aca="false">IF(D37="Внутри модуля",0,MAX(0,L37-Q37))</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="S37" s="3" t="n">
         <f aca="false">R37*P37</f>
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>213</v>
+        <v>99</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="G38" s="3" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>217</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="I38" s="3"/>
       <c r="J38" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L38" s="3" t="n">
         <f aca="false">J38*K38</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N38" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3" t="n">
@@ -4442,44 +4549,42 @@
       </c>
       <c r="R38" s="3" t="n">
         <f aca="false">IF(D38="Внутри модуля",0,MAX(0,L38-Q38))</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="S38" s="3" t="n">
         <f aca="false">R38*P38</f>
         <v>0</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="V38" s="3" t="s">
-        <v>219</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="V38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="n">
@@ -4493,10 +4598,10 @@
         <v>8</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O39" s="3"/>
       <c r="P39" s="3" t="n">
@@ -4514,54 +4619,54 @@
         <v>0</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>118</v>
+        <v>229</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L40" s="3" t="n">
         <f aca="false">J40*K40</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O40" s="3"/>
       <c r="P40" s="3" t="n">
@@ -4572,59 +4677,61 @@
       </c>
       <c r="R40" s="3" t="n">
         <f aca="false">IF(D40="Внутри модуля",0,MAX(0,L40-Q40))</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S40" s="3" t="n">
         <f aca="false">R40*P40</f>
         <v>0</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="V40" s="3"/>
+        <v>150</v>
+      </c>
+      <c r="V40" s="3" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>118</v>
+        <v>229</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L41" s="3" t="n">
         <f aca="false">J41*K41</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O41" s="3"/>
       <c r="P41" s="3" t="n">
@@ -4635,61 +4742,61 @@
       </c>
       <c r="R41" s="3" t="n">
         <f aca="false">IF(D41="Внутри модуля",0,MAX(0,L41-Q41))</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S41" s="3" t="n">
         <f aca="false">R41*P41</f>
         <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3" t="s">
-        <v>234</v>
+        <v>67</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L42" s="3" t="n">
         <f aca="false">J42*K42</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="O42" s="3"/>
       <c r="P42" s="3" t="n">
@@ -4700,65 +4807,69 @@
       </c>
       <c r="R42" s="3" t="n">
         <f aca="false">IF(D42="Внутри модуля",0,MAX(0,L42-Q42))</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S42" s="3" t="n">
         <f aca="false">R42*P42</f>
         <v>0</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I43" s="3"/>
+        <v>135</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>244</v>
+      </c>
       <c r="J43" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L43" s="3" t="n">
         <f aca="false">J43*K43</f>
         <v>4</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="O43" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>245</v>
+      </c>
       <c r="P43" s="3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>0</v>
@@ -4769,57 +4880,57 @@
       </c>
       <c r="S43" s="3" t="n">
         <f aca="false">R43*P43</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>93</v>
+        <v>246</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E44" s="3"/>
-      <c r="F44" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>27</v>
+        <v>190</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I44" s="3"/>
+        <v>135</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>250</v>
+      </c>
       <c r="J44" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L44" s="3" t="n">
         <f aca="false">J44*K44</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>218</v>
+        <v>251</v>
       </c>
       <c r="O44" s="3"/>
       <c r="P44" s="3" t="n">
@@ -4830,7 +4941,7 @@
       </c>
       <c r="R44" s="3" t="n">
         <f aca="false">IF(D44="Внутри модуля",0,MAX(0,L44-Q44))</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="S44" s="3" t="n">
         <f aca="false">R44*P44</f>
@@ -4840,105 +4951,101 @@
         <v>32</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>93</v>
+        <v>252</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L45" s="3" t="n">
         <f aca="false">J45*K45</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="O45" s="4" t="s">
-        <v>248</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="O45" s="3"/>
       <c r="P45" s="3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R45" s="3" t="n">
         <f aca="false">IF(D45="Внутри модуля",0,MAX(0,L45-Q45))</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S45" s="3" t="n">
         <f aca="false">R45*P45</f>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>250</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="V45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>259</v>
+      </c>
       <c r="G46" s="3" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>253</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="I46" s="3"/>
       <c r="J46" s="3" t="n">
         <v>1</v>
       </c>
@@ -4950,10 +5057,10 @@
         <v>1</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="O46" s="3"/>
       <c r="P46" s="3" t="n">
@@ -4974,37 +5081,35 @@
         <v>32</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>255</v>
+        <v>150</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E47" s="3"/>
-      <c r="F47" s="3" t="s">
-        <v>259</v>
-      </c>
+      <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>1</v>
@@ -5017,10 +5122,10 @@
         <v>1</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>244</v>
+        <v>45</v>
       </c>
       <c r="O47" s="3"/>
       <c r="P47" s="3" t="n">
@@ -5041,32 +5146,34 @@
         <v>32</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="V47" s="3"/>
+        <v>139</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="n">
@@ -5080,10 +5187,10 @@
         <v>1</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="O48" s="3"/>
       <c r="P48" s="3" t="n">
@@ -5104,36 +5211,36 @@
         <v>32</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
+      <c r="F49" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="G49" s="3" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>267</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="I49" s="3"/>
       <c r="J49" s="3" t="n">
         <v>1</v>
       </c>
@@ -5145,10 +5252,10 @@
         <v>1</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="O49" s="3"/>
       <c r="P49" s="3" t="n">
@@ -5169,28 +5276,28 @@
         <v>32</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>143</v>
+        <v>246</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>265</v>
+        <v>23</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>27</v>
@@ -5213,9 +5320,11 @@
         <v>29</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O50" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>277</v>
+      </c>
       <c r="P50" s="3" t="n">
         <v>0</v>
       </c>
@@ -5234,28 +5343,28 @@
         <v>32</v>
       </c>
       <c r="U50" s="3" t="s">
-        <v>249</v>
+        <v>33</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>265</v>
+        <v>23</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>27</v>
@@ -5275,14 +5384,16 @@
         <v>1</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O51" s="3"/>
+        <v>39</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>282</v>
+      </c>
       <c r="P51" s="3" t="n">
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="Q51" s="3" t="n">
         <v>0</v>
@@ -5293,40 +5404,40 @@
       </c>
       <c r="S51" s="3" t="n">
         <f aca="false">R51*P51</f>
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="T51" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="n">
@@ -5345,9 +5456,7 @@
       <c r="N52" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="O52" s="4" t="s">
-        <v>280</v>
-      </c>
+      <c r="O52" s="3"/>
       <c r="P52" s="3" t="n">
         <v>0</v>
       </c>
@@ -5366,31 +5475,31 @@
         <v>32</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>23</v>
+        <v>241</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>28</v>
@@ -5407,16 +5516,14 @@
         <v>1</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>285</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="O53" s="3"/>
       <c r="P53" s="3" t="n">
-        <v>790</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="3" t="n">
         <v>0</v>
@@ -5427,40 +5534,40 @@
       </c>
       <c r="S53" s="3" t="n">
         <f aca="false">R53*P53</f>
-        <v>790</v>
+        <v>0</v>
       </c>
       <c r="T53" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>286</v>
+        <v>33</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="n">
@@ -5474,14 +5581,16 @@
         <v>1</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="O54" s="3"/>
+        <v>296</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>297</v>
+      </c>
       <c r="P54" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q54" s="3" t="n">
         <v>0</v>
@@ -5492,57 +5601,57 @@
       </c>
       <c r="S54" s="3" t="n">
         <f aca="false">R54*P54</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>244</v>
+        <v>131</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L55" s="3" t="n">
         <f aca="false">J55*K55</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="O55" s="3"/>
       <c r="P55" s="3" t="n">
@@ -5553,7 +5662,7 @@
       </c>
       <c r="R55" s="3" t="n">
         <f aca="false">IF(D55="Внутри модуля",0,MAX(0,L55-Q55))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S55" s="3" t="n">
         <f aca="false">R55*P55</f>
@@ -5563,28 +5672,28 @@
         <v>32</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>33</v>
+        <v>302</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>27</v>
@@ -5604,16 +5713,16 @@
         <v>1</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>299</v>
+        <v>30</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="3" t="n">
         <v>0</v>
@@ -5624,59 +5733,61 @@
       </c>
       <c r="S56" s="3" t="n">
         <f aca="false">R56*P56</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T56" s="3" t="s">
         <v>32</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L57" s="3" t="n">
         <f aca="false">J57*K57</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="O57" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>312</v>
+      </c>
       <c r="P57" s="3" t="n">
         <v>0</v>
       </c>
@@ -5685,7 +5796,7 @@
       </c>
       <c r="R57" s="3" t="n">
         <f aca="false">IF(D57="Внутри модуля",0,MAX(0,L57-Q57))</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S57" s="3" t="n">
         <f aca="false">R57*P57</f>
@@ -5695,28 +5806,28 @@
         <v>32</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>305</v>
+        <v>85</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>27</v>
@@ -5726,23 +5837,23 @@
       </c>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L58" s="3" t="n">
         <f aca="false">J58*K58</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>29</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="P58" s="3" t="n">
         <v>0</v>
@@ -5752,7 +5863,7 @@
       </c>
       <c r="R58" s="3" t="n">
         <f aca="false">IF(D58="Внутри модуля",0,MAX(0,L58-Q58))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S58" s="3" t="n">
         <f aca="false">R58*P58</f>
@@ -5762,26 +5873,290 @@
         <v>32</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>286</v>
+        <v>85</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>311</v>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <f aca="false">J59*K59</f>
+        <v>2</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <f aca="false">IF(D59="Внутри модуля",0,MAX(0,L59-Q59))</f>
+        <v>2</v>
+      </c>
+      <c r="S59" s="3" t="n">
+        <f aca="false">R59*P59</f>
+        <v>0</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <f aca="false">J60*K60</f>
+        <v>1</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <f aca="false">IF(D60="Внутри модуля",0,MAX(0,L60-Q60))</f>
+        <v>1</v>
+      </c>
+      <c r="S60" s="3" t="n">
+        <f aca="false">R60*P60</f>
+        <v>0</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <f aca="false">J61*K61</f>
+        <v>1</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <f aca="false">IF(D61="Внутри модуля",0,MAX(0,L61-Q61))</f>
+        <v>1</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <f aca="false">R61*P61</f>
+        <v>0</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U61" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V61" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <f aca="false">J62*K62</f>
+        <v>1</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <f aca="false">IF(D62="Внутри модуля",0,MAX(0,L62-Q62))</f>
+        <v>1</v>
+      </c>
+      <c r="S62" s="3" t="n">
+        <f aca="false">R62*P62</f>
+        <v>0</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:V500">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$H2="Предложение"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$H2="Уточняется"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$G2="Только функция"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T500">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$T2="Да"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5818,23 +6193,12 @@
   <hyperlinks>
     <hyperlink ref="O2" r:id="rId1" display="https://www.chipdip.ru/product/gst220a24-r7b-blok-pitaniya-24b-9.2a-221vt-mean-well-9000420376"/>
     <hyperlink ref="O3" r:id="rId2" display="https://ozon.ru/t/zLw6TpD"/>
-    <hyperlink ref="O6" r:id="rId3" display="https://ozon.ru/t/1fZdgL1"/>
-    <hyperlink ref="O7" r:id="rId4" display="https://ozon.ru/t/gmtx6pg"/>
-    <hyperlink ref="O8" r:id="rId5" display="https://ozon.ru/t/v0TomWG"/>
-    <hyperlink ref="O9" r:id="rId6" display="https://ozon.ru/t/1fZdgL1"/>
-    <hyperlink ref="O10" r:id="rId7" display="https://ozon.ru/t/QWYR5Dy"/>
-    <hyperlink ref="O14" r:id="rId8" display="https://ozon.ru/t/Wcg9F9p"/>
-    <hyperlink ref="O16" r:id="rId9" display="https://ozon.ru/t/QWYQvBC"/>
-    <hyperlink ref="O18" r:id="rId10" display="https://ozon.ru/t/3QXN2ZT"/>
-    <hyperlink ref="O19" r:id="rId11" display="https://ozon.ru/t/gmtx6pg"/>
-    <hyperlink ref="O22" r:id="rId12" display="https://ozon.ru/t/tPvFr4r"/>
-    <hyperlink ref="O27" r:id="rId13" display="https://ozon.ru/t/sXzB21l"/>
-    <hyperlink ref="O28" r:id="rId14" display="https://ozon.ru/t/QWYR5Dy"/>
-    <hyperlink ref="O29" r:id="rId15" display="https://ozon.ru/t/ukwD77G"/>
-    <hyperlink ref="O30" r:id="rId16" display="https://ozon.ru/t/1fZ9B9H"/>
-    <hyperlink ref="O37" r:id="rId17" display="https://www.chipdip.ru/product/nrp-02-c-05dh-rele-1-pereklyuch-5vdc-3a-125vac-spdt-na-ncr-9000276611"/>
-    <hyperlink ref="O45" r:id="rId18" display="https://market.yandex.ru/cc/AwZszU"/>
-    <hyperlink ref="O52" r:id="rId19" display="https://www.chipdip.ru/product/nrp-15-c-24d"/>
+    <hyperlink ref="O8" r:id="rId3" display="https://ozon.ru/t/QWYR5Dy"/>
+    <hyperlink ref="O14" r:id="rId4" display="https://ozon.ru/t/QWYQvBC"/>
+    <hyperlink ref="O16" r:id="rId5" display="https://ozon.ru/t/3QXN2ZT"/>
+    <hyperlink ref="O18" r:id="rId6" display="https://ozon.ru/t/sXzB21l"/>
+    <hyperlink ref="O27" r:id="rId7" display="https://ozon.ru/t/ukwD77G"/>
+    <hyperlink ref="O28" r:id="rId8" display="https://ozon.ru/t/1fZ9B9H"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5844,7 +6208,7 @@
     <oddFooter/>
   </headerFooter>
   <tableParts>
-    <tablePart r:id="rId20"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5873,28 +6237,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>14</v>
@@ -5905,7 +6269,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>23</v>
@@ -5914,10 +6278,10 @@
         <v>28</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="G2" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A2,Компоненты!$A:$A,0)),"")</f>
@@ -5937,10 +6301,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>23</v>
@@ -5949,10 +6313,10 @@
         <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="G3" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A3,Компоненты!$A:$A,0)),"")</f>
@@ -5967,27 +6331,27 @@
         <v>1</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="G4" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A4,Компоненты!$A:$A,0)),"")</f>
@@ -6002,27 +6366,27 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="G5" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A5,Компоненты!$A:$A,0)),"")</f>
@@ -6037,27 +6401,27 @@
         <v>0</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="G6" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A6,Компоненты!$A:$A,0)),"")</f>
@@ -6072,27 +6436,27 @@
         <v>0</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="G7" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A7,Компоненты!$A:$A,0)),"")</f>
@@ -6107,27 +6471,27 @@
         <v>0</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="G8" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A8,Компоненты!$A:$A,0)),"")</f>
@@ -6145,22 +6509,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="G9" s="3" t="n">
         <f aca="false">IFERROR(INDEX(Компоненты!$L:$L,MATCH(A9,Компоненты!$A:$A,0)),"")</f>
@@ -6175,12 +6539,12 @@
         <v>4</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>341</v>
+      <c r="A11" s="6" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -6211,7 +6575,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
@@ -6223,323 +6587,343 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>345</v>
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>350</v>
+      <c r="C2" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>350</v>
+      <c r="A3" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>350</v>
+      <c r="A4" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>362</v>
+      <c r="A5" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>350</v>
+      <c r="A6" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>350</v>
+      <c r="A7" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>350</v>
+      <c r="A8" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>350</v>
-      </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>143</v>
+      <c r="A10" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>387</v>
+      <c r="A11" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>387</v>
+      <c r="A12" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>350</v>
+      <c r="A13" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="A14" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>350</v>
+      <c r="C14" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>387</v>
+      <c r="A15" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="B16" s="7" t="s">
+      <c r="A16" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>387</v>
+      <c r="C16" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -6571,423 +6955,423 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
-        <v>408</v>
+      <c r="A1" s="9" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="B3" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$H:$H,A4)</f>
-        <v>34</v>
-      </c>
-      <c r="C4" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="C4" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$H:$H,A4)</f>
-        <v>84</v>
-      </c>
-      <c r="D4" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="D4" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$R:$R,Компоненты!$H:$H,A4)</f>
-        <v>66</v>
-      </c>
-      <c r="E4" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="E4" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$H:$H,A4)</f>
-        <v>9623</v>
+        <v>9476</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="10" t="n">
+      <c r="A5" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$H:$H,A5)</f>
-        <v>13</v>
-      </c>
-      <c r="C5" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$H:$H,A5)</f>
-        <v>58</v>
-      </c>
-      <c r="D5" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="D5" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$R:$R,Компоненты!$H:$H,A5)</f>
-        <v>58</v>
-      </c>
-      <c r="E5" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$H:$H,A5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="10" t="n">
+      <c r="A6" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B6" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$H:$H,A6)</f>
         <v>10</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$H:$H,A6)</f>
         <v>51</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$R:$R,Компоненты!$H:$H,A6)</f>
         <v>35</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$H:$H,A6)</f>
         <v>1032</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="B7" s="11" t="n">
+      <c r="A7" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B7" s="12" t="n">
         <f aca="false">SUM(B4:B6)</f>
-        <v>57</v>
-      </c>
-      <c r="C7" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C7" s="12" t="n">
         <f aca="false">SUM(C4:C6)</f>
-        <v>193</v>
-      </c>
-      <c r="D7" s="11" t="n">
+        <v>204</v>
+      </c>
+      <c r="D7" s="12" t="n">
         <f aca="false">SUM(D4:D6)</f>
-        <v>159</v>
-      </c>
-      <c r="E7" s="11" t="n">
+        <v>170</v>
+      </c>
+      <c r="E7" s="12" t="n">
         <f aca="false">SUM(E4:E6)</f>
-        <v>10655</v>
+        <v>10508</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="A10" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A11)</f>
-        <v>16</v>
-      </c>
-      <c r="C11" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A11)</f>
-        <v>16</v>
-      </c>
-      <c r="D11" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A11,Компоненты!$H:$H,"Уточняется")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$B:$B,A11)</f>
-        <v>7514</v>
+        <v>7367</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B12" s="10" t="n">
+      <c r="A12" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A12)</f>
         <v>2</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A12)</f>
         <v>3</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A12,Компоненты!$H:$H,"Уточняется")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$B:$B,A12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="B13" s="10" t="n">
+      <c r="A13" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A13)</f>
         <v>14</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A13)</f>
         <v>67</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A13,Компоненты!$H:$H,"Уточняется")</f>
         <v>4</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$B:$B,A13)</f>
         <v>1086</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" s="10" t="n">
+      <c r="A14" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A14)</f>
         <v>9</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A14)</f>
         <v>65</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A14,Компоненты!$H:$H,"Уточняется")</f>
         <v>1</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$B:$B,A14)</f>
         <v>1455</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="10" t="n">
+      <c r="A15" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A15)</f>
         <v>5</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C15" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A15)</f>
         <v>18</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A15,Компоненты!$H:$H,"Уточняется")</f>
         <v>1</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$B:$B,A15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B16" s="10" t="n">
+      <c r="A16" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A16)</f>
         <v>3</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A16)</f>
         <v>13</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A16,Компоненты!$H:$H,"Уточняется")</f>
         <v>0</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$B:$B,A16)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="B17" s="10" t="n">
+      <c r="A17" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B17" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A17)</f>
         <v>5</v>
       </c>
-      <c r="C17" s="10" t="n">
+      <c r="C17" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A17)</f>
         <v>8</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A17,Компоненты!$H:$H,"Уточняется")</f>
         <v>3</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$B:$B,A17)</f>
         <v>600</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="B18" s="10" t="n">
+      <c r="A18" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A18)</f>
         <v>3</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A18)</f>
         <v>3</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$B:$B,A18,Компоненты!$H:$H,"Уточняется")</f>
         <v>1</v>
       </c>
-      <c r="E18" s="10" t="n">
+      <c r="E18" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$S:$S,Компоненты!$B:$B,A18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="B19" s="11" t="n">
+      <c r="A19" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B19" s="12" t="n">
         <f aca="false">SUM(B11:B18)</f>
-        <v>57</v>
-      </c>
-      <c r="C19" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C19" s="12" t="n">
         <f aca="false">SUM(C11:C18)</f>
-        <v>193</v>
-      </c>
-      <c r="D19" s="11" t="n">
+        <v>204</v>
+      </c>
+      <c r="D19" s="12" t="n">
         <f aca="false">SUM(D11:D18)</f>
         <v>10</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <f aca="false">SUM(E11:E18)</f>
-        <v>10655</v>
+        <v>10508</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>409</v>
+      <c r="B22" s="10" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$G:$G,A23)</f>
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="B24" s="10" t="n">
+      <c r="A24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$G:$G,A24)</f>
         <v>12</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="10" t="n">
+      <c r="A25" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B25" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$G:$G,A25)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>410</v>
+      <c r="B27" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$D:$D,A28)</f>
         <v>8</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$D:$D,A28)</f>
         <v>20</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="10" t="n">
+      <c r="B29" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$D:$D,A29)</f>
-        <v>45</v>
-      </c>
-      <c r="C29" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="C29" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$D:$D,A29)</f>
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B30" s="10" t="n">
+      <c r="A30" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$D:$D,A30)</f>
         <v>4</v>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C30" s="11" t="n">
         <f aca="false">SUMIFS(Компоненты!$L:$L,Компоненты!$D:$D,A30)</f>
         <v>20</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="B32" s="10" t="n">
+      <c r="A32" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="B32" s="11" t="n">
         <f aca="false">COUNTIFS(Компоненты!$T:$T,"Да")</f>
         <v>7</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="B33" s="10" t="n">
+      <c r="A33" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="B33" s="11" t="n">
         <f aca="false">COUNTA(Отклонено!$A:$A)-1</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>416</v>
+      <c r="A35" s="6" t="s">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -7013,150 +7397,150 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>417</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="E1" s="12" t="s">
+      <c r="C1" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="12" t="s">
-        <v>418</v>
+      <c r="G1" s="13" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>100</v>
+      <c r="F2" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" s="13" t="s">
+      <c r="C3" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="14" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>141</v>
+      <c r="E4" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="A5" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>218</v>
+      <c r="F5" s="14" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>254</v>
+      <c r="A6" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="F7" s="13" t="s">
+      <c r="A7" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>244</v>
+      <c r="A8" s="14" t="s">
+        <v>241</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
-        <v>265</v>
+      <c r="A9" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F10" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F11" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>419</v>
+      <c r="A12" s="6" t="s">
+        <v>449</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>30</v>
@@ -7164,7 +7548,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F14" s="1" t="s">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>

--- a/bom/Component_Base.xlsx
+++ b/bom/Component_Base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misha/Documents/BMSTU/Master/Manipulator/electronics/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0557ED-C287-5A47-9569-2FA7BBFFDCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DA25FE-8C0B-8442-92FA-C3EB0BA2EFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="483">
   <si>
     <t>ID</t>
   </si>
@@ -1405,6 +1405,90 @@
   </si>
   <si>
     <t>https://ozon.ru/t/3 QXN2ZT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МЛТ-0,25 ±5 %, 150 Ом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МЛТ-0,25 ±5 %, 4,7 кОм (подтяжка к 3,3 В)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МЛТ-0,25 ±5 %, 10 кОм (подтяжка к 3,3 В)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МЛТ-0,25 ±5 %, 1 кОм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МЛТ-0,25 ±5 %, 470 Ом (LED, от шины KH 5 В, ~8 мА) + 10 кОм (подтяжка GPIO41 к 3,3 В)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МЛТ-0,25 ±5 %, 220 Ом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МЛТ-0,25 ±5 %, 4,7 кОм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С2-23-0,25 ±1 %, делитель 10 кОм + 20 кОм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МЛТ-0,25 ±5 %, 100 Ом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С2-23-0,25 ±1 %, делитель 10 кОм + 20 кОм на линии ESP-RX (5 В → 3,3 В)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МЛТ-0,25 ±5 %, 10 кОм (подтяжка к 3,3 В) + конденсатор керамический 0,1 мкФ 50 В X7R (фильтр дребезга)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Клемма приборная ZP-001, винтовой зажим и гнездо «банан» 4 мм, 15 А (красная и чёрная)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разъём межплатного шлейфа 2×6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вилка IDC BH-12 (DS1013-12SIB), на плату, 2×6, шаг 2,54 мм, с ключом, 1 А</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чат 05.10 (утверждено Mikhail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC X6…X9 (4 шт.) и CH X1 (1 шт.); в схемах поле BaseID не проставлено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гнёзда под модуль контроллера</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гнездо PBS-22 (DS1023-1×22), однорядное, 22 контакта, шаг 2,54 мм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC XS1, XS2 — пара гнёзд под модуль; в схемах поле BaseID не проставлено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разъём сигнальный 5 контактов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JST B5B-XH-A (LF)(SN), вилка прямая на плату, XH, 2,5 мм, 5 контактов, 3 А</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LR X1…X4 (4 шт.) и CH X2 (1 шт.); в схемах поле BaseID не проставлено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">чат 06.10 (утверждено Mikhail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LR X1…X8 (8 шт.) и CH X2 (1 шт.); позиция клемм ZP-001 (E-051) исключена 06.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PS X2 (кнопка питания), MC X1 и X2, MC X10, LR X9 — вилка на 4 контакта; PS X2 и MC X2 переключены с E-018 06.10.2026</t>
   </si>
 </sst>
 </file>
@@ -1664,11 +1748,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Components" displayName="Components" ref="A1:V63" totalsRowShown="0">
-  <autoFilter ref="A1:V63" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Components" displayName="Components" ref="A1:V65" totalsRowShown="0">
+  <autoFilter ref="A1:V65" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="13">
       <filters>
-        <filter val="Режим ЛР"/>
+        <filter val="CH"/>
+        <filter val="LR"/>
+        <filter val="MC"/>
+        <filter val="PS"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1913,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -2208,7 +2295,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>48</v>
       </c>
@@ -2273,7 +2360,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>54</v>
       </c>
@@ -2407,7 +2494,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>65</v>
       </c>
@@ -2422,7 +2509,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>455</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>27</v>
@@ -2474,7 +2561,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -2539,7 +2626,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>75</v>
       </c>
@@ -2604,7 +2691,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>81</v>
       </c>
@@ -2671,7 +2758,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>87</v>
       </c>
@@ -2738,7 +2825,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>95</v>
       </c>
@@ -2753,7 +2840,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>97</v>
+        <v>456</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>27</v>
@@ -2803,7 +2890,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>100</v>
       </c>
@@ -2870,7 +2957,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>106</v>
       </c>
@@ -2885,7 +2972,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>108</v>
+        <v>457</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>27</v>
@@ -2935,7 +3022,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
@@ -3017,7 +3104,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>118</v>
+        <v>458</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>27</v>
@@ -3149,7 +3236,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>127</v>
+        <v>459</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>27</v>
@@ -3199,7 +3286,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>130</v>
       </c>
@@ -3266,7 +3353,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>137</v>
       </c>
@@ -3333,7 +3420,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>142</v>
       </c>
@@ -3398,7 +3485,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>147</v>
       </c>
@@ -3413,7 +3500,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>149</v>
+        <v>460</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>27</v>
@@ -3463,7 +3550,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>151</v>
       </c>
@@ -3478,7 +3565,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>153</v>
+        <v>461</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>27</v>
@@ -3528,7 +3615,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>155</v>
       </c>
@@ -3595,7 +3682,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>160</v>
       </c>
@@ -3610,7 +3697,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>455</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>27</v>
@@ -3662,7 +3749,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>163</v>
       </c>
@@ -3729,7 +3816,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>168</v>
       </c>
@@ -3796,7 +3883,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>174</v>
       </c>
@@ -3863,7 +3950,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>179</v>
       </c>
@@ -3878,7 +3965,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>181</v>
+        <v>462</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>27</v>
@@ -4160,7 +4247,7 @@
         <v>4</v>
       </c>
       <c r="L34" s="2">
-        <f t="shared" ref="L34:L65" si="3">J34*K34</f>
+        <f t="shared" ref="L34:L63" si="3">J34*K34</f>
         <v>8</v>
       </c>
       <c r="M34" s="2" t="s">
@@ -4177,11 +4264,11 @@
         <v>0</v>
       </c>
       <c r="R34" s="2">
-        <f t="shared" ref="R34:R65" si="4">IF(D34="Внутри модуля",0,MAX(0,L34-Q34))</f>
+        <f t="shared" ref="R34:R63" si="4">IF(D34="Внутри модуля",0,MAX(0,L34-Q34))</f>
         <v>0</v>
       </c>
       <c r="S34" s="2">
-        <f t="shared" ref="S34:S65" si="5">R34*P34</f>
+        <f t="shared" ref="S34:S63" si="5">R34*P34</f>
         <v>0</v>
       </c>
       <c r="T34" s="2" t="s">
@@ -4263,20 +4350,20 @@
     </row>
     <row r="36" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>209</v>
+        <v>476</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>210</v>
+        <v>477</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>211</v>
+        <v>478</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>27</v>
@@ -4286,14 +4373,14 @@
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K36" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <f>J36*K36</f>
+        <v>9</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>78</v>
@@ -4309,21 +4396,21 @@
         <v>0</v>
       </c>
       <c r="R36" s="2">
-        <f t="shared" si="4"/>
-        <v>20</v>
+        <f>L36-Q36</f>
+        <v>9</v>
       </c>
       <c r="S36" s="2">
-        <f t="shared" si="5"/>
+        <f>R36*P36</f>
         <v>0</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>128</v>
+        <v>480</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>213</v>
+        <v>481</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4341,7 +4428,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>216</v>
+        <v>463</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>27</v>
@@ -4521,7 +4608,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>226</v>
       </c>
@@ -4586,7 +4673,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>231</v>
       </c>
@@ -4651,7 +4738,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>236</v>
       </c>
@@ -4666,7 +4753,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2" t="s">
-        <v>67</v>
+        <v>455</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>27</v>
@@ -4915,7 +5002,7 @@
       </c>
       <c r="V45" s="2"/>
     </row>
-    <row r="46" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>256</v>
       </c>
@@ -4930,7 +5017,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>258</v>
+        <v>464</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>27</v>
@@ -5175,7 +5262,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="50" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>273</v>
       </c>
@@ -5309,7 +5396,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="52" spans="1:22" ht="45.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:22" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>284</v>
       </c>
@@ -5374,7 +5461,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="53" spans="1:22" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:22" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>288</v>
       </c>
@@ -5506,7 +5593,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="55" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>298</v>
       </c>
@@ -5521,7 +5608,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>300</v>
+        <v>465</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>27</v>
@@ -5638,7 +5725,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="57" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>307</v>
       </c>
@@ -5705,7 +5792,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="58" spans="1:22" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:22" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>312</v>
       </c>
@@ -5772,7 +5859,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="59" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>317</v>
       </c>
@@ -5839,7 +5926,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="60" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>322</v>
       </c>
@@ -5864,7 +5951,7 @@
       </c>
       <c r="I60" s="2"/>
       <c r="J60" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K60" s="2">
         <v>1</v>
@@ -5903,10 +5990,10 @@
         <v>85</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>327</v>
       </c>
@@ -5971,7 +6058,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="62" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>331</v>
       </c>
@@ -6036,7 +6123,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="63" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>335</v>
       </c>
@@ -6099,6 +6186,136 @@
       </c>
       <c r="V63" s="2" t="s">
         <v>338</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2">
+        <v>5</v>
+      </c>
+      <c r="K64" s="2">
+        <v>1</v>
+      </c>
+      <c r="L64" s="2">
+        <f>J64*K64</f>
+        <v>5</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>0</v>
+      </c>
+      <c r="R64" s="2">
+        <f>L64-Q64</f>
+        <v>5</v>
+      </c>
+      <c r="S64" s="2">
+        <f>R64*P64</f>
+        <v>0</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2">
+        <v>2</v>
+      </c>
+      <c r="K65" s="2">
+        <v>1</v>
+      </c>
+      <c r="L65" s="2">
+        <f>J65*K65</f>
+        <v>2</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>0</v>
+      </c>
+      <c r="R65" s="2">
+        <f>L65-Q65</f>
+        <v>2</v>
+      </c>
+      <c r="S65" s="2">
+        <f>R65*P65</f>
+        <v>0</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>475</v>
       </c>
     </row>
   </sheetData>

--- a/bom/Component_Base.xlsx
+++ b/bom/Component_Base.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misha/Documents/BMSTU/Master/Manipulator/electronics/bom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DA25FE-8C0B-8442-92FA-C3EB0BA2EFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42632B7E-AEA9-9B48-B585-29C379C9D144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17280" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="465">
   <si>
     <t>ID</t>
   </si>
@@ -243,9 +243,6 @@
     <t>Резистор индикатора +5P</t>
   </si>
   <si>
-    <t>150 Ом</t>
-  </si>
-  <si>
     <t>https://ozon.ru/t/QWYR5Dy</t>
   </si>
   <si>
@@ -333,9 +330,6 @@
     <t>Подтяжки главной шины I2C</t>
   </si>
   <si>
-    <t>4,7 кОм на 3,3 В</t>
-  </si>
-  <si>
     <t>чат 20.09 (утверждено Mikhail)</t>
   </si>
   <si>
@@ -366,9 +360,6 @@
     <t>Подтяжка RST мультиплексора</t>
   </si>
   <si>
-    <t>10 кОм на 3,3 В</t>
-  </si>
-  <si>
     <t>чат 15.09</t>
   </si>
   <si>
@@ -396,9 +387,6 @@
     <t>Подтяжка шины KH на землю</t>
   </si>
   <si>
-    <t>1 кОм</t>
-  </si>
-  <si>
     <t>https://ozon.ru/t/gmtx6pg</t>
   </si>
   <si>
@@ -423,9 +411,6 @@
     <t>Резисторы оптореле KH</t>
   </si>
   <si>
-    <t>470 Ом (LED, от шины KH 5 В, ~8 мА) + 10 кОм (подтяжка GPIO41 к 3,3 В)</t>
-  </si>
-  <si>
     <t>чат 19.09 (утверждено Mikhail)</t>
   </si>
   <si>
@@ -489,9 +474,6 @@
     <t>Резистор LED 6N137</t>
   </si>
   <si>
-    <t>220 Ом</t>
-  </si>
-  <si>
     <t>Общий для ESP32 (3,3 В) и студента (3,3/5 В)</t>
   </si>
   <si>
@@ -501,9 +483,6 @@
     <t>Подтяжка выхода 6N137 к +5P</t>
   </si>
   <si>
-    <t>4,7 кОм</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Утверждено 19.09.2026 в составе силовой части.</t>
   </si>
   <si>
@@ -585,9 +564,6 @@
     <t>Согласование выхода ACS712 с ADC ESP32</t>
   </si>
   <si>
-    <t>Делитель 10 кОм + 20 кОм</t>
-  </si>
-  <si>
     <t>0–5 В → 0–3,3 В; не утверждено Утверждено 19.09.2026 вместе с силовой частью.</t>
   </si>
   <si>
@@ -669,30 +645,15 @@
     <t>Катушки от шины KH (+5P), ~40 мА каждая; сторона — граница: катушки от +5P, контакты в логических цепях</t>
   </si>
   <si>
-    <t>E-051</t>
-  </si>
-  <si>
-    <t>Клеммы разъёма внешнего управления звеном</t>
-  </si>
-  <si>
-    <t>Комбинированные приборные клеммы: винт + гнездо «банан» 4 мм</t>
-  </si>
-  <si>
     <t>LR</t>
   </si>
   <si>
-    <t>Раскладка 2×3: SCL, SDA, GND / IN1, IN2, пусто. Варианты (банан 4 мм, приборные, барьерные) отложены. Разъём на логической земле Тип согласован 19.09.2026; конкретная модель добирается при закупке.</t>
-  </si>
-  <si>
     <t>E-052</t>
   </si>
   <si>
     <t>Защита SDA/SCL разъёма ЛР — последовательный резистор</t>
   </si>
   <si>
-    <t>100 Ом</t>
-  </si>
-  <si>
     <t>Решение «добавить защиту» принято, номиналы — предложение Утверждено 19.09.2026 вместе с разъёмом ЛР.</t>
   </si>
   <si>
@@ -816,9 +777,6 @@
     <t>Защита линии ESP-RX от 5-вольтового передатчика</t>
   </si>
   <si>
-    <t>Делитель 10 кОм + 20 кОм на линии ESP-RX (5 В → 3,3 В)</t>
-  </si>
-  <si>
     <t>Контроллер схвата не выбран (3,3 или 5 В) Утверждено 20.09.2026: на разъём схвата выводится +5 В логики, контроллер схвата может оказаться 5-вольтовым, поэтому защита входа ESP32 обязательна независимо от его выбора. Номиналы приняты как у E-040; при переходе схвата на 3,3 В делитель можно заменить перемычкой.</t>
   </si>
   <si>
@@ -942,9 +900,6 @@
     <t>Обвязка концевика M1</t>
   </si>
   <si>
-    <t>10 кОм (подтяжка к 3,3 В) + 100 нФ (фильтр дребезга)</t>
-  </si>
-  <si>
     <t>Вход ESP32 — GPIO48 из резерва (предложение, «Аккуратно!» в распиновке); обработка по прерыванию Утверждено 20.09.2026; GPIO48 остаётся пометкой «Аккуратно!» в распиновке, к выбору компонента не относится.</t>
   </si>
   <si>
@@ -1020,9 +975,6 @@
     <t>https://www.chipdip.ru/product/b4b-xh-a-lf-sn-razem-shtyrevoy-4-kontakta-2.5mm-na-jst-9000628021</t>
   </si>
   <si>
-    <t>XP1: 1 — катушка K1 (A2), 2 — GND_P (контакт кнопки замыкает 1–2), 3 — подсветка GND_P, 4 — подсветка +24V после реле. Ответная часть на кабель: корпус XHP-4 + контакты SXH-001T-P0.6 ×4 — докупить. Цена не заполнена</t>
-  </si>
-  <si>
     <t>E-093</t>
   </si>
   <si>
@@ -1407,88 +1359,82 @@
     <t>https://ozon.ru/t/3 QXN2ZT</t>
   </si>
   <si>
-    <t xml:space="preserve">МЛТ-0,25 ±5 %, 150 Ом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МЛТ-0,25 ±5 %, 4,7 кОм (подтяжка к 3,3 В)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МЛТ-0,25 ±5 %, 10 кОм (подтяжка к 3,3 В)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МЛТ-0,25 ±5 %, 1 кОм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МЛТ-0,25 ±5 %, 470 Ом (LED, от шины KH 5 В, ~8 мА) + 10 кОм (подтяжка GPIO41 к 3,3 В)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МЛТ-0,25 ±5 %, 220 Ом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МЛТ-0,25 ±5 %, 4,7 кОм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">С2-23-0,25 ±1 %, делитель 10 кОм + 20 кОм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МЛТ-0,25 ±5 %, 100 Ом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">С2-23-0,25 ±1 %, делитель 10 кОм + 20 кОм на линии ESP-RX (5 В → 3,3 В)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">МЛТ-0,25 ±5 %, 10 кОм (подтяжка к 3,3 В) + конденсатор керамический 0,1 мкФ 50 В X7R (фильтр дребезга)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Клемма приборная ZP-001, винтовой зажим и гнездо «банан» 4 мм, 15 А (красная и чёрная)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Разъём межплатного шлейфа 2×6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Вилка IDC BH-12 (DS1013-12SIB), на плату, 2×6, шаг 2,54 мм, с ключом, 1 А</t>
-  </si>
-  <si>
-    <t xml:space="preserve">чат 05.10 (утверждено Mikhail)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MC X6…X9 (4 шт.) и CH X1 (1 шт.); в схемах поле BaseID не проставлено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гнёзда под модуль контроллера</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гнездо PBS-22 (DS1023-1×22), однорядное, 22 контакта, шаг 2,54 мм</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MC XS1, XS2 — пара гнёзд под модуль; в схемах поле BaseID не проставлено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Разъём сигнальный 5 контактов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JST B5B-XH-A (LF)(SN), вилка прямая на плату, XH, 2,5 мм, 5 контактов, 3 А</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LR X1…X4 (4 шт.) и CH X2 (1 шт.); в схемах поле BaseID не проставлено</t>
-  </si>
-  <si>
-    <t xml:space="preserve">чат 06.10 (утверждено Mikhail)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LR X1…X8 (8 шт.) и CH X2 (1 шт.); позиция клемм ZP-001 (E-051) исключена 06.10.2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PS X2 (кнопка питания), MC X1 и X2, MC X10, LR X9 — вилка на 4 контакта; PS X2 и MC X2 переключены с E-018 06.10.2026</t>
+    <t>МЛТ-0,25 ±5 %, 150 Ом</t>
+  </si>
+  <si>
+    <t>МЛТ-0,25 ±5 %, 4,7 кОм (подтяжка к 3,3 В)</t>
+  </si>
+  <si>
+    <t>МЛТ-0,25 ±5 %, 10 кОм (подтяжка к 3,3 В)</t>
+  </si>
+  <si>
+    <t>МЛТ-0,25 ±5 %, 1 кОм</t>
+  </si>
+  <si>
+    <t>МЛТ-0,25 ±5 %, 470 Ом (LED, от шины KH 5 В, ~8 мА) + 10 кОм (подтяжка GPIO41 к 3,3 В)</t>
+  </si>
+  <si>
+    <t>МЛТ-0,25 ±5 %, 220 Ом</t>
+  </si>
+  <si>
+    <t>МЛТ-0,25 ±5 %, 4,7 кОм</t>
+  </si>
+  <si>
+    <t>С2-23-0,25 ±1 %, делитель 10 кОм + 20 кОм</t>
+  </si>
+  <si>
+    <t>МЛТ-0,25 ±5 %, 100 Ом</t>
+  </si>
+  <si>
+    <t>С2-23-0,25 ±1 %, делитель 10 кОм + 20 кОм на линии ESP-RX (5 В → 3,3 В)</t>
+  </si>
+  <si>
+    <t>МЛТ-0,25 ±5 %, 10 кОм (подтяжка к 3,3 В) + конденсатор керамический 0,1 мкФ 50 В X7R (фильтр дребезга)</t>
+  </si>
+  <si>
+    <t>E-096</t>
+  </si>
+  <si>
+    <t>Разъём межплатного шлейфа 2×6</t>
+  </si>
+  <si>
+    <t>Вилка IDC BH-12 (DS1013-12SIB), на плату, 2×6, шаг 2,54 мм, с ключом, 1 А</t>
+  </si>
+  <si>
+    <t>чат 05.10 (утверждено Mikhail)</t>
+  </si>
+  <si>
+    <t>MC X6…X9 (4 шт.) и CH X1 (1 шт.); в схемах поле BaseID не проставлено</t>
+  </si>
+  <si>
+    <t>E-097</t>
+  </si>
+  <si>
+    <t>Гнёзда под модуль контроллера</t>
+  </si>
+  <si>
+    <t>Гнездо PBS-22 (DS1023-1×22), однорядное, 22 контакта, шаг 2,54 мм</t>
+  </si>
+  <si>
+    <t>MC XS1, XS2 — пара гнёзд под модуль; в схемах поле BaseID не проставлено</t>
+  </si>
+  <si>
+    <t>E-098</t>
+  </si>
+  <si>
+    <t>Разъём сигнальный 5 контактов</t>
+  </si>
+  <si>
+    <t>JST B5B-XH-A (LF)(SN), вилка прямая на плату, XH, 2,5 мм, 5 контактов, 3 А</t>
+  </si>
+  <si>
+    <t>чат 06.10 (утверждено Mikhail)</t>
+  </si>
+  <si>
+    <t>LR X1…X8 (8 шт.) и CH X2 (1 шт.); позиция клемм ZP-001 (E-051) исключена 06.10.2026</t>
+  </si>
+  <si>
+    <t>PS X2 (кнопка питания), MC X1 и X2, MC X10, LR X9 — вилка на 4 контакта; PS X2 и MC X2 переключены с E-018 06.10.2026</t>
   </si>
 </sst>
 </file>
@@ -1749,16 +1695,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Components" displayName="Components" ref="A1:V65" totalsRowShown="0">
-  <autoFilter ref="A1:V65" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="13">
-      <filters>
-        <filter val="CH"/>
-        <filter val="LR"/>
-        <filter val="MC"/>
-        <filter val="PS"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:V65" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Узел"/>
@@ -2094,7 +2031,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -2161,7 +2098,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>35</v>
       </c>
@@ -2228,7 +2165,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>42</v>
       </c>
@@ -2427,7 +2364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>60</v>
       </c>
@@ -2509,7 +2446,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>27</v>
@@ -2535,7 +2472,7 @@
         <v>51</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P8" s="2">
         <v>84</v>
@@ -2558,25 +2495,25 @@
         <v>58</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>27</v>
@@ -2596,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>51</v>
@@ -2623,25 +2560,25 @@
         <v>33</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>27</v>
@@ -2661,10 +2598,10 @@
         <v>1</v>
       </c>
       <c r="M10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" s="2">
@@ -2688,25 +2625,25 @@
         <v>33</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>27</v>
@@ -2732,7 +2669,7 @@
         <v>51</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P11" s="2">
         <v>0</v>
@@ -2752,28 +2689,28 @@
         <v>32</v>
       </c>
       <c r="U11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="V11" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>27</v>
@@ -2793,13 +2730,13 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="N12" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="O12" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P12" s="2">
         <v>966</v>
@@ -2816,31 +2753,31 @@
         <v>0</v>
       </c>
       <c r="T12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U12" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>27</v>
@@ -2860,10 +2797,10 @@
         <v>2</v>
       </c>
       <c r="M13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2">
@@ -2884,28 +2821,28 @@
         <v>32</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>27</v>
@@ -2925,13 +2862,13 @@
         <v>1</v>
       </c>
       <c r="M14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="N14" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="O14" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="P14" s="2">
         <v>518</v>
@@ -2951,28 +2888,28 @@
         <v>32</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V14" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>27</v>
@@ -2992,10 +2929,10 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" s="2">
@@ -3016,28 +2953,28 @@
         <v>32</v>
       </c>
       <c r="U15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="V15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>27</v>
@@ -3063,7 +3000,7 @@
         <v>39</v>
       </c>
       <c r="O16" s="14" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="P16" s="2">
         <v>487</v>
@@ -3086,25 +3023,25 @@
         <v>33</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>27</v>
@@ -3127,10 +3064,10 @@
         <v>29</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="P17" s="2">
         <v>79</v>
@@ -3156,20 +3093,20 @@
     </row>
     <row r="18" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>27</v>
@@ -3189,13 +3126,13 @@
         <v>1</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="P18" s="2">
         <v>73</v>
@@ -3218,25 +3155,25 @@
         <v>33</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>27</v>
@@ -3256,10 +3193,10 @@
         <v>2</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" s="2">
@@ -3280,28 +3217,28 @@
         <v>32</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>27</v>
@@ -3324,10 +3261,10 @@
         <v>29</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="P20" s="2">
         <v>0</v>
@@ -3347,30 +3284,30 @@
         <v>32</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>27</v>
@@ -3393,7 +3330,7 @@
         <v>29</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" s="2">
@@ -3414,28 +3351,28 @@
         <v>32</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>27</v>
@@ -3455,10 +3392,10 @@
         <v>8</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" s="2">
@@ -3479,28 +3416,28 @@
         <v>32</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>27</v>
@@ -3520,10 +3457,10 @@
         <v>8</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" s="2">
@@ -3544,28 +3481,28 @@
         <v>32</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>27</v>
@@ -3588,7 +3525,7 @@
         <v>29</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2">
@@ -3609,28 +3546,28 @@
         <v>32</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>27</v>
@@ -3650,13 +3587,13 @@
         <v>4</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="P25" s="2">
         <v>73</v>
@@ -3676,28 +3613,28 @@
         <v>32</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>27</v>
@@ -3717,13 +3654,13 @@
         <v>4</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P26" s="2">
         <v>84</v>
@@ -3743,28 +3680,28 @@
         <v>32</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>27</v>
@@ -3787,10 +3724,10 @@
         <v>29</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="P27" s="2">
         <v>108</v>
@@ -3810,28 +3747,28 @@
         <v>32</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>27</v>
@@ -3851,13 +3788,13 @@
         <v>4</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="P28" s="2">
         <v>130</v>
@@ -3877,30 +3814,30 @@
         <v>32</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>27</v>
@@ -3920,10 +3857,10 @@
         <v>4</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" s="2">
@@ -3944,28 +3881,28 @@
         <v>32</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>27</v>
@@ -3985,10 +3922,10 @@
         <v>8</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" s="2">
@@ -4009,28 +3946,28 @@
         <v>32</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>27</v>
@@ -4053,10 +3990,10 @@
         <v>29</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>187</v>
+        <v>178</v>
+      </c>
+      <c r="O31" s="14" t="s">
+        <v>179</v>
       </c>
       <c r="P31" s="2">
         <v>2184</v>
@@ -4073,31 +4010,31 @@
         <v>8736</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>27</v>
@@ -4117,10 +4054,10 @@
         <v>4</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2">
@@ -4141,30 +4078,30 @@
         <v>32</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>27</v>
@@ -4184,10 +4121,10 @@
         <v>4</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" s="2">
@@ -4208,36 +4145,36 @@
         <v>32</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2">
@@ -4251,10 +4188,10 @@
         <v>8</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" s="2">
@@ -4275,28 +4212,28 @@
         <v>32</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>27</v>
@@ -4316,13 +4253,13 @@
         <v>16</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="P35" s="2">
         <v>51</v>
@@ -4342,28 +4279,28 @@
         <v>32</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>27</v>
@@ -4383,10 +4320,10 @@
         <v>9</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" s="2">
@@ -4407,28 +4344,28 @@
         <v>32</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>27</v>
@@ -4448,10 +4385,10 @@
         <v>8</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2">
@@ -4469,31 +4406,31 @@
         <v>0</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U37" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V37" s="2" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>27</v>
@@ -4513,10 +4450,10 @@
         <v>8</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2">
@@ -4534,31 +4471,31 @@
         <v>0</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U38" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>27</v>
@@ -4578,10 +4515,10 @@
         <v>8</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" s="2">
@@ -4599,31 +4536,31 @@
         <v>0</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>27</v>
@@ -4643,10 +4580,10 @@
         <v>1</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2">
@@ -4664,34 +4601,34 @@
         <v>0</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>28</v>
@@ -4708,10 +4645,10 @@
         <v>4</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" s="2">
@@ -4729,31 +4666,31 @@
         <v>0</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>27</v>
@@ -4773,10 +4710,10 @@
         <v>8</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2">
@@ -4797,37 +4734,37 @@
         <v>32</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="J43" s="2">
         <v>4</v>
@@ -4840,13 +4777,13 @@
         <v>4</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="P43" s="2">
         <v>150</v>
@@ -4866,21 +4803,21 @@
         <v>32</v>
       </c>
       <c r="U43" s="2" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>37</v>
@@ -4888,13 +4825,13 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="J44" s="2">
         <v>1</v>
@@ -4910,7 +4847,7 @@
         <v>30</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" s="2">
@@ -4931,37 +4868,37 @@
         <v>32</v>
       </c>
       <c r="U44" s="2" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="V44" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="J45" s="2">
         <v>1</v>
@@ -4977,7 +4914,7 @@
         <v>29</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" s="2">
@@ -4998,26 +4935,26 @@
         <v>32</v>
       </c>
       <c r="U45" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="V45" s="2"/>
     </row>
     <row r="46" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>27</v>
@@ -5037,10 +4974,10 @@
         <v>1</v>
       </c>
       <c r="M46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N46" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" s="2">
@@ -5061,21 +4998,21 @@
         <v>32</v>
       </c>
       <c r="U46" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>37</v>
@@ -5083,13 +5020,13 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="J47" s="2">
         <v>1</v>
@@ -5102,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>45</v>
@@ -5126,28 +5063,28 @@
         <v>32</v>
       </c>
       <c r="U47" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="2" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>27</v>
@@ -5191,28 +5128,28 @@
         <v>32</v>
       </c>
       <c r="U48" s="2" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>27</v>
@@ -5232,7 +5169,7 @@
         <v>1</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>30</v>
@@ -5256,28 +5193,28 @@
         <v>32</v>
       </c>
       <c r="U49" s="2" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="V49" s="2" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>27</v>
@@ -5303,7 +5240,7 @@
         <v>51</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="P50" s="2">
         <v>0</v>
@@ -5326,25 +5263,25 @@
         <v>33</v>
       </c>
       <c r="V50" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="2" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>27</v>
@@ -5370,7 +5307,7 @@
         <v>39</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="P51" s="2">
         <v>790</v>
@@ -5390,28 +5327,28 @@
         <v>32</v>
       </c>
       <c r="U51" s="2" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="V51" s="2" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
     </row>
     <row r="52" spans="1:22" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>27</v>
@@ -5455,28 +5392,28 @@
         <v>32</v>
       </c>
       <c r="U52" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="V52" s="2" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="1:22" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>27</v>
@@ -5496,10 +5433,10 @@
         <v>1</v>
       </c>
       <c r="M53" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N53" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" s="2">
@@ -5523,25 +5460,25 @@
         <v>33</v>
       </c>
       <c r="V53" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>27</v>
@@ -5561,13 +5498,13 @@
         <v>1</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="P54" s="2">
         <v>26</v>
@@ -5587,28 +5524,28 @@
         <v>32</v>
       </c>
       <c r="U54" s="2" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
     </row>
     <row r="55" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>27</v>
@@ -5628,10 +5565,10 @@
         <v>2</v>
       </c>
       <c r="M55" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N55" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" s="2">
@@ -5652,28 +5589,28 @@
         <v>32</v>
       </c>
       <c r="U55" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" ht="57" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>27</v>
@@ -5699,7 +5636,7 @@
         <v>30</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="P56" s="2">
         <v>0</v>
@@ -5719,28 +5656,28 @@
         <v>32</v>
       </c>
       <c r="U56" s="2" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>27</v>
@@ -5766,7 +5703,7 @@
         <v>51</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="P57" s="2">
         <v>0</v>
@@ -5786,28 +5723,28 @@
         <v>32</v>
       </c>
       <c r="U57" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>27</v>
@@ -5833,7 +5770,7 @@
         <v>51</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="P58" s="2">
         <v>0</v>
@@ -5853,28 +5790,28 @@
         <v>32</v>
       </c>
       <c r="U58" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>27</v>
@@ -5894,13 +5831,13 @@
         <v>2</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>51</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="P59" s="2">
         <v>0</v>
@@ -5920,28 +5857,28 @@
         <v>32</v>
       </c>
       <c r="U59" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
     </row>
     <row r="60" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>27</v>
@@ -5958,7 +5895,7 @@
       </c>
       <c r="L60" s="2">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>29</v>
@@ -5967,7 +5904,7 @@
         <v>51</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="P60" s="2">
         <v>0</v>
@@ -5977,7 +5914,7 @@
       </c>
       <c r="R60" s="2">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S60" s="2">
         <f t="shared" si="5"/>
@@ -5987,31 +5924,31 @@
         <v>32</v>
       </c>
       <c r="U60" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
     </row>
     <row r="61" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>28</v>
@@ -6052,31 +5989,31 @@
         <v>32</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>28</v>
@@ -6117,31 +6054,31 @@
         <v>32</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
     </row>
     <row r="63" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="2" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>28</v>
@@ -6158,10 +6095,10 @@
         <v>4</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" s="2">
@@ -6182,28 +6119,28 @@
         <v>32</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>338</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="2" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>27</v>
@@ -6223,10 +6160,10 @@
         <v>5</v>
       </c>
       <c r="M64" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N64" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2">
@@ -6247,28 +6184,28 @@
         <v>32</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
     </row>
     <row r="65" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="2" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>27</v>
@@ -6288,10 +6225,10 @@
         <v>2</v>
       </c>
       <c r="M65" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N65" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="N65" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="2">
@@ -6312,10 +6249,10 @@
         <v>32</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -6344,11 +6281,12 @@
     <hyperlink ref="O18" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="O27" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
     <hyperlink ref="O28" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="O31" r:id="rId9" xr:uid="{7EA5B2D8-5369-574C-B7D5-42980F0196B2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -6443,28 +6381,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>339</v>
+        <v>323</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>14</v>
@@ -6475,7 +6413,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -6484,10 +6422,10 @@
         <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="G2" s="2">
         <f>IFERROR(INDEX(Компоненты!$L:$L,MATCH(A2,Компоненты!$A:$A,0)),"")</f>
@@ -6510,7 +6448,7 @@
         <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>23</v>
@@ -6519,10 +6457,10 @@
         <v>28</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="G3" s="2">
         <f>IFERROR(INDEX(Компоненты!$L:$L,MATCH(A3,Компоненты!$A:$A,0)),"")</f>
@@ -6542,22 +6480,22 @@
     </row>
     <row r="4" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="G4" s="2">
         <f>IFERROR(INDEX(Компоненты!$L:$L,MATCH(A4,Компоненты!$A:$A,0)),"")</f>
@@ -6572,27 +6510,27 @@
         <v>0</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="G5" s="2">
         <f>IFERROR(INDEX(Компоненты!$L:$L,MATCH(A5,Компоненты!$A:$A,0)),"")</f>
@@ -6607,27 +6545,27 @@
         <v>0</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="G6" s="2">
         <f>IFERROR(INDEX(Компоненты!$L:$L,MATCH(A6,Компоненты!$A:$A,0)),"")</f>
@@ -6642,27 +6580,27 @@
         <v>0</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="G7" s="2">
         <f>IFERROR(INDEX(Компоненты!$L:$L,MATCH(A7,Компоненты!$A:$A,0)),"")</f>
@@ -6677,27 +6615,27 @@
         <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="G8" s="2">
         <f>IFERROR(INDEX(Компоненты!$L:$L,MATCH(A8,Компоненты!$A:$A,0)),"")</f>
@@ -6715,22 +6653,22 @@
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="G9" s="2">
         <f>IFERROR(INDEX(Компоненты!$L:$L,MATCH(A9,Компоненты!$A:$A,0)),"")</f>
@@ -6745,12 +6683,12 @@
         <v>4</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -6792,336 +6730,336 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -7146,7 +7084,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7154,13 +7092,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>18</v>
@@ -7172,7 +7110,7 @@
       </c>
       <c r="B4" s="10">
         <f>COUNTIFS(Компоненты!$H:$H,A4)</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" s="10">
         <f>SUMIFS(Компоненты!$L:$L,Компоненты!$H:$H,A4)</f>
@@ -7189,7 +7127,7 @@
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="B5" s="10">
         <f>COUNTIFS(Компоненты!$H:$H,A5)</f>
@@ -7210,7 +7148,7 @@
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B6" s="10">
         <f>COUNTIFS(Компоненты!$H:$H,A6)</f>
@@ -7231,11 +7169,11 @@
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="B7" s="11">
         <f>SUM(B4:B6)</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C7" s="11">
         <f>SUM(C4:C6)</f>
@@ -7255,13 +7193,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>18</v>
@@ -7277,7 +7215,7 @@
       </c>
       <c r="C11" s="10">
         <f>SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A11)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D11" s="10">
         <f>COUNTIFS(Компоненты!$B:$B,A11,Компоненты!$H:$H,"Уточняется")</f>
@@ -7290,15 +7228,15 @@
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B12" s="10">
         <f>COUNTIFS(Компоненты!$B:$B,A12)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C12" s="10">
         <f>SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A12)</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D12" s="10">
         <f>COUNTIFS(Компоненты!$B:$B,A12,Компоненты!$H:$H,"Уточняется")</f>
@@ -7311,7 +7249,7 @@
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B13" s="10">
         <f>COUNTIFS(Компоненты!$B:$B,A13)</f>
@@ -7332,7 +7270,7 @@
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B14" s="10">
         <f>COUNTIFS(Компоненты!$B:$B,A14)</f>
@@ -7340,7 +7278,7 @@
       </c>
       <c r="C14" s="10">
         <f>SUMIFS(Компоненты!$L:$L,Компоненты!$B:$B,A14)</f>
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D14" s="10">
         <f>COUNTIFS(Компоненты!$B:$B,A14,Компоненты!$H:$H,"Уточняется")</f>
@@ -7353,7 +7291,7 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B15" s="10">
         <f>COUNTIFS(Компоненты!$B:$B,A15)</f>
@@ -7374,7 +7312,7 @@
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="B16" s="10">
         <f>COUNTIFS(Компоненты!$B:$B,A16)</f>
@@ -7395,7 +7333,7 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="B17" s="10">
         <f>COUNTIFS(Компоненты!$B:$B,A17)</f>
@@ -7416,7 +7354,7 @@
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B18" s="10">
         <f>COUNTIFS(Компоненты!$B:$B,A18)</f>
@@ -7437,11 +7375,11 @@
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="B19" s="11">
         <f>SUM(B11:B18)</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C19" s="11">
         <f>SUM(C11:C18)</f>
@@ -7461,7 +7399,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7470,12 +7408,12 @@
       </c>
       <c r="B23" s="10">
         <f>COUNTIFS(Компоненты!$G:$G,A23)</f>
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B24" s="10">
         <f>COUNTIFS(Компоненты!$G:$G,A24)</f>
@@ -7484,7 +7422,7 @@
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="B25" s="10">
         <f>COUNTIFS(Компоненты!$G:$G,A25)</f>
@@ -7496,10 +7434,10 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7521,7 +7459,7 @@
       </c>
       <c r="B29" s="10">
         <f>COUNTIFS(Компоненты!$D:$D,A29)</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C29" s="10">
         <f>SUMIFS(Компоненты!$L:$L,Компоненты!$D:$D,A29)</f>
@@ -7530,7 +7468,7 @@
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B30" s="10">
         <f>COUNTIFS(Компоненты!$D:$D,A30)</f>
@@ -7543,16 +7481,16 @@
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="B32" s="10">
         <f>COUNTIFS(Компоненты!$T:$T,"Да")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="B33" s="10">
         <f>COUNTA(Отклонено!$A:$A)-1</f>
@@ -7561,7 +7499,7 @@
     </row>
     <row r="35" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -7586,10 +7524,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>340</v>
+        <v>324</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>12</v>
@@ -7598,7 +7536,7 @@
         <v>13</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7618,27 +7556,27 @@
         <v>29</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>37</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>51</v>
@@ -7649,46 +7587,46 @@
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>30</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>39</v>
@@ -7696,7 +7634,7 @@
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="F8" t="s">
         <v>45</v>
@@ -7704,25 +7642,25 @@
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="F9" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F10" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F11" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="F12" t="s">
         <v>30</v>
@@ -7730,7 +7668,7 @@
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F14" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>

--- a/bom/Component_Base.xlsx
+++ b/bom/Component_Base.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Сводка" sheetId="4" r:id="rId4"/>
     <sheet name="Справочники" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1694,8 +1694,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Components" displayName="Components" ref="A1:V65" totalsRowShown="0">
-  <autoFilter ref="A1:V65" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Components" displayName="Components" ref="A1:V67" totalsRowShown="0">
+  <autoFilter ref="A1:V67" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Узел"/>
@@ -1937,7 +1937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -2038,15 +2038,19 @@
       <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>24</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Блок питания 220 → 24 В</t>
+        </is>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>26</v>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean Well LRS-600-24, 24 В, 25 А, 600 Вт (встраиваемый, с вентилятором)</t>
+        </is>
       </c>
       <c r="G2" s="2" t="s">
         <v>27</v>
@@ -2071,11 +2075,13 @@
       <c r="N2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>31</v>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.chipdip.ru/product/lrs-600-24-blok-pitaniya-24v-25a-600vt-mean-well-9001070782</t>
+        </is>
       </c>
       <c r="P2" s="2">
-        <v>5860</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2">
         <v>0</v>
@@ -2088,14 +2094,20 @@
         <f t="shared" ref="S2:S33" si="2">R2*P2</f>
         <v>5860</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>34</v>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вариант motor-fga: расчётный ток стенда ≈ 21 А (4 × 4,5 А FGA + схват 2 А + логика ~0,9 А), запас ~16 %. 220 В доходит до блока: размещение (внутри стенда или отдельный бокс с PE) требует решения — «ноутбучная» схема в этом варианте не действует. Вход блока — клеммы под сетевой провод. Пусковой ток FGA ограничивать в ПО (разгон ШИМ, отключение по ACS712). Цену уточнить. Было (main): GST220A24-R7B, 9,2 А.</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2179,8 +2191,10 @@
         <v>37</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
-        <v>44</v>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Предохранитель флажковый (ATO) 25 А + держатель на провод с крышкой АЭНК 8219 (до 30 А)</t>
+        </is>
       </c>
       <c r="G4" s="2" t="s">
         <v>27</v>
@@ -2225,11 +2239,15 @@
       <c r="T4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>47</v>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Внутри корпуса, врезается в линию +24 между разъёмом ввода и реле NRP-15. Вариант motor-fga: 25 А под LRS-600-24, провод участка ввода 12 AWG. Было (main): 10 А. Цена держателя не заполнена</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2360,8 +2378,10 @@
       <c r="U6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>59</v>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выставить 5,0 В и зафиксировать; питает ТОЛЬКО +5P: катушки NRP-02 ×16 (~640 мА), оптореле, выходы 6N137; вариант motor-fga — также логика IBT-2 ×4 (VCC 5 В, ток уточнить). Остров — от E-010</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3237,8 +3257,10 @@
         <v>25</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="2" t="s">
-        <v>128</v>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Модуль IBT-2 (2 × BTS7960), 5,5–27,5 В (абс. 45 В), ограничение тока ≥ 33 А, логика 5 В</t>
+        </is>
       </c>
       <c r="G20" s="2" t="s">
         <v>27</v>
@@ -3263,14 +3285,12 @@
       <c r="N20" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>130</v>
-      </c>
+      <c r="O20" s="3"/>
       <c r="P20" s="2">
         <v>0</v>
       </c>
       <c r="Q20" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" s="2">
         <f t="shared" si="1"/>
@@ -3280,14 +3300,20 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U20" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>131</v>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вариант motor-fga, под FGA (4,5 А ном., ~20 А стоп.). Управление: RPWM = IN1, LPWM = IN2 (выходы 6N137 с подтяжками к +5P), R_EN и L_EN — к +5P, VCC — +5P, GND — GND_P; R_IS, L_IS не используются (силовая сторона). 10 — вперёд, 01 — назад, 11 и 00 — торможение: выбега нет, учесть в ПО. ШИМ ≤ 25 кГц (20 кГц проходит). Модуль ~40 × 50 мм с радиатором — на стойках рядом с CH, сигналы шлейфом 6 проводов, питание и мотор — проводами к клеммникам модуля. Распиновку и шаг гребёнки сверить на модуле; ссылку и цену уточнить. Было (main): DRV8871, модули есть 4 шт.</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3306,8 +3332,10 @@
       <c r="E21" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>135</v>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BTS7960B</t>
+        </is>
       </c>
       <c r="G21" s="2" t="s">
         <v>27</v>
@@ -3317,7 +3345,7 @@
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="2">
         <v>4</v>
@@ -3350,11 +3378,15 @@
       <c r="T21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U21" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>136</v>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Приходит с модулем E-030 (2 шт. на модуль)</t>
+        </is>
       </c>
     </row>
     <row r="22" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3700,8 +3732,10 @@
         <v>37</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="2" t="s">
-        <v>158</v>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NRP-15-A-24D (NCR), катушка 24 В 39 мА / 0,93 Вт, контакт 1A (NO) 30 А</t>
+        </is>
       </c>
       <c r="G27" s="2" t="s">
         <v>27</v>
@@ -3726,11 +3760,13 @@
       <c r="N27" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>159</v>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.chipdip.by/product/nrp-15-a-24d</t>
+        </is>
       </c>
       <c r="P27" s="2">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="2">
         <v>0</v>
@@ -3746,11 +3782,15 @@
       <c r="T27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U27" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>160</v>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вариант motor-fga: рвёт +24V_M модуля IBT-2. Катушка — от +24V через КР293КП2Б (230 В, 120 мА, 10 Ом): вывод ключа U3 переносится с +5P на +24V; параллельно катушке — диод E-099. Номинал контакта 1A по постоянному току сверить по datasheet NCR NRP15; разрыв стопорного тока — аварийный случай, штатно ПО сначала снимает R_EN/L_EN. Было (main): HF49FD/005-1H11, 5 А.</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3767,8 +3807,10 @@
         <v>25</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="2" t="s">
-        <v>163</v>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACS712-30A (модуль), 66 мВ/А</t>
+        </is>
       </c>
       <c r="G28" s="2" t="s">
         <v>27</v>
@@ -3793,14 +3835,12 @@
       <c r="N28" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="O28" s="3" t="s">
-        <v>164</v>
-      </c>
+      <c r="O28" s="3"/>
       <c r="P28" s="2">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R28" s="2">
         <f t="shared" si="1"/>
@@ -3813,11 +3853,15 @@
       <c r="T28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U28" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>166</v>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сигнальная часть — логические +5; измеряемая цепь — силовая. Вариант motor-fga: ±30 А; делитель R6/R7 (×2/3) без изменений: 0,79–2,55 В на АЦП при ±20 А, 0,35–2,99 В при ±30 А (44 мВ/А). Размеры модуля сверить с ACS712-20A. Ссылку и цену уточнить. Было (main): ACS712-20A, есть 4 шт.</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3836,8 +3880,10 @@
       <c r="E29" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>169</v>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACS712ELCTR-30A</t>
+        </is>
       </c>
       <c r="G29" s="2" t="s">
         <v>27</v>
@@ -3880,8 +3926,10 @@
       <c r="T29" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U29" s="2" t="s">
-        <v>170</v>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
       </c>
       <c r="V29" s="2" t="s">
         <v>171</v>
@@ -3966,8 +4014,10 @@
         <v>37</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="2" t="s">
-        <v>177</v>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Мотор-редуктор StepperOnline FGA-43246000-G149 (прямозубый, 149:1) со штатным 43-мм мотором 24 В: 4,5 А ном., ~20 А стоп.</t>
+        </is>
       </c>
       <c r="G31" s="2" t="s">
         <v>27</v>
@@ -3992,11 +4042,9 @@
       <c r="N31" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="O31" s="14" t="s">
-        <v>179</v>
-      </c>
+      <c r="O31" s="14"/>
       <c r="P31" s="2">
-        <v>2184</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="2">
         <v>0</v>
@@ -4012,11 +4060,15 @@
       <c r="T31" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="U31" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>180</v>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вариант motor-fga (утверждено 20.10.2026): куплен — количество и цену уточнить; токи (4,5 А ном., ~20 А стоп.) сверить по паспорту. Определяет драйвер E-030, реле E-037, датчик E-038, блок питания E-001, кольцо E-080 (6 силовых дорожек ≥ 5 А), ширины меди CH и PS. Было (main): червячный NFP-5840-31ZY-DSH, ≤ 1,2 А.</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4310,7 +4362,7 @@
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K36" s="2">
         <v>1</v>
@@ -4346,8 +4398,10 @@
       <c r="U36" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="V36" s="2" t="s">
-        <v>463</v>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LR X1…X8 (8 шт.) и CH X2 (1 шт.); позиция клемм ZP-001 (E-051) исключена 06.10.2026. Вариант motor-fga: + CH X6 (шлейф к модулю IBT-2: RPWM, LPWM, EN, +5P, GND_P) — 1 шт. на плату CH; на стороне модуля — корпус Dupont 2 × 4 (шаг 2,54) по шелкографии IBT-2</t>
+        </is>
       </c>
     </row>
     <row r="37" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5065,8 +5119,10 @@
       <c r="U47" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="V47" s="2" t="s">
-        <v>250</v>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Дорожки: 6 силовых (M2…M4, ток по мотору) + I2C и +5/GND энкодеров + 6–7 схвата; силовые и логические дорожки раздельно. Вариант motor-fga: силовые M2…M4 — 6 дорожек ≥ 5 А длительно (FGA 4,5 А ном.), схват — 2 по 2 А</t>
+        </is>
       </c>
     </row>
     <row r="48" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5213,8 +5269,10 @@
         <v>37</v>
       </c>
       <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
-        <v>261</v>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NRP-15-A-24D (NCR), катушка 24 В DC 619 Ом / 39 мА / 0,93 Вт, контакт 1A (NO): 30 А</t>
+        </is>
       </c>
       <c r="G50" s="2" t="s">
         <v>27</v>
@@ -5239,8 +5297,10 @@
       <c r="N50" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="O50" s="3" t="s">
-        <v>262</v>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.chipdip.by/product/nrp-15-a-24d</t>
+        </is>
       </c>
       <c r="P50" s="2">
         <v>0</v>
@@ -5259,11 +5319,15 @@
       <c r="T50" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U50" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V50" s="2" t="s">
-        <v>263</v>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контакт COM–NO рвёт шину +24 после предохранителя; A1 — +24V_IN постоянно, A2 — на GND_P через контакт кнопки E-002. Вариант motor-fga: ток шины ≈ 21 А больше 20 А контакта 1C — нужно исполнение 1A; номинал 1A по постоянному току сверить по datasheet NCR NRP15. Footprint Relay_NRP-15_1C: у исполнения A нет NC — площадка 5 не используется (сверить чертёж). Было (main): NRP-15-C-24D.</t>
+        </is>
       </c>
     </row>
     <row r="51" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5273,18 +5337,24 @@
       <c r="B51" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>265</v>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разъём ввода 24 В на корпусе (от блока питания)</t>
+        </is>
       </c>
       <c r="D51" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E51" s="2"/>
-      <c r="F51" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>27</v>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XT60 (30 А): гнездо на корпусе + вилка на кабель блока питания — модель требует подбора</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кандидат</t>
+        </is>
       </c>
       <c r="H51" s="2" t="s">
         <v>28</v>
@@ -5306,11 +5376,9 @@
       <c r="N51" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="O51" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="O51" s="2"/>
       <c r="P51" s="2">
-        <v>790</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="2">
         <v>0</v>
@@ -5326,11 +5394,15 @@
       <c r="T51" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U51" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>269</v>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вариант motor-fga: KPJX-PM-4S (2 × 7,5 А = 15 А) не проходит по току 21–25 А. Кабель блок питания → корпус 12 AWG. Было (main): Kycon KPJX-PM-4S.</t>
+        </is>
       </c>
     </row>
     <row r="52" spans="1:22" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5658,8 +5730,10 @@
       <c r="U56" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="V56" s="2" t="s">
-        <v>291</v>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вход адаптера GST220A — C14, шнур в комплект не входит; ток от сети ~1 А. Вариант motor-fga: у LRS-600-24 вход — клеммы, шнур C13 не подходит; сетевой провод 3 × 0,75–1 мм² с вилкой — уточнить вместе с размещением блока. Цена не заполнена</t>
+        </is>
       </c>
     </row>
     <row r="57" spans="1:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5669,8 +5743,10 @@
       <c r="B57" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>293</v>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Клеммник силовых линий 24 В на плате PS (выходы X6…X10)</t>
+        </is>
       </c>
       <c r="D57" s="2" t="s">
         <v>37</v>
@@ -5687,7 +5763,7 @@
       </c>
       <c r="I57" s="2"/>
       <c r="J57" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K57" s="2">
         <v>1</v>
@@ -5722,11 +5798,15 @@
       <c r="T57" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U57" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="V57" s="2" t="s">
-        <v>296</v>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выходы +24 X6…X10 по 4,5 А — DG301 (15 А) подходит, провод к CH — 18 AWG. Вариант motor-fga: ввод X1 — отдельный клеммник E-100 (ток 21–25 А, провод 2,5–4 мм² в DG301 не входит). По чертежу Degson 200102539: корпус 5,0×N × 7,6 × 10 мм, вывод ⌀1,0, отверстие 1,2 (в footprint 1,3), винт M2.5, момент 0,29 Н·м. Ответная часть не нужна; полярность — шёлкографией; стыкуются в ряд</t>
+        </is>
       </c>
     </row>
     <row r="58" spans="1:22" ht="57" customHeight="1" x14ac:dyDescent="0.2">
@@ -6253,6 +6333,178 @@
       </c>
       <c r="V65" s="2" t="s">
         <v>458</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-099</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Канал привода</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Диод параллельно катушке реле K5 (E-037)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Компонент</t>
+        </is>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1N4007 (катодом к +24V)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выбран</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Утверждено</t>
+        </is>
+      </c>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2">
+        <v>1</v>
+      </c>
+      <c r="K66" s="2">
+        <v>4</v>
+      </c>
+      <c r="L66" s="2">
+        <f>J66*K66</f>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Силовая</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CH</t>
+        </is>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>0</v>
+      </c>
+      <c r="R66" s="2">
+        <f>IF(D66="Внутри модуля",0,MAX(0,L66-Q66))</f>
+      </c>
+      <c r="S66" s="2">
+        <f>R66*P66</f>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вариант motor-fga: катушка 24 В коммутируется КР293КП2Б — диод гасит выброс при размыкании.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-100</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Питание</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Клеммник ввода +24 на плате PS (X1)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Компонент</t>
+        </is>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DG301-5.0-04P-12 (Degson) — клеммник винтовой на плату, 4 контакта, шаг 5,0 мм, 15 А на контакт: по 2 контакта на полюс</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Кандидат</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Утверждено</t>
+        </is>
+      </c>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2">
+        <v>1</v>
+      </c>
+      <c r="K67" s="2">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2">
+        <f>J67*K67</f>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Силовая</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PS</t>
+        </is>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>0</v>
+      </c>
+      <c r="R67" s="2">
+        <f>IF(D67="Внутри модуля",0,MAX(0,L67-Q67))</f>
+      </c>
+      <c r="S67" s="2">
+        <f>R67*P67</f>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вариант motor-fga: ввод +24 на PS (X1), ток 21–25 А: контакты 1, 2 — +24V_IN, 3, 4 — GND_P (2 × 15 А на полюс), провод 2 × 1,5 мм² на полюс. Тип — как клеммник на модуле IBT-2 (фото Mikhail 20.10.2026); наличие 4-контактного исполнения сверить. Выходы X6…X10 — DG301-5.0-02P (E-017).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6412,8 +6664,10 @@
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>329</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean Well LRS-600-24 (блок 24 В, 25 А, 600 Вт)</t>
+        </is>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -6421,11 +6675,15 @@
       <c r="D2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>331</v>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вход 115/230 В AC (переключатель), защиты КЗ/перегрузки/перенапряжения/перегрева, вентилятор, подстройка выхода</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Разъём XT60 E-014, предохранитель 25 А E-003, реле E-013 + диод E-015, кнопка E-002</t>
+        </is>
       </c>
       <c r="G2" s="2">
         <f>IFERROR(INDEX(Компоненты!$L:$L,MATCH(A2,Компоненты!$A:$A,0)),"")</f>
@@ -6439,8 +6697,10 @@
         <f>IFERROR(INDEX(Компоненты!$R:$R,MATCH(A2,Компоненты!$A:$A,0)),"")</f>
         <v>1</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>31</v>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.chipdip.ru/product/lrs-600-24-blok-pitaniya-24v-25a-600vt-mean-well-9001070782</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6552,20 +6812,28 @@
       <c r="A6" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>341</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IBT-2 (2 × BTS7960)</t>
+        </is>
       </c>
       <c r="C6" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>343</v>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Утверждено</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BTS7960B ×2, буфер входов, радиатор, клеммники B+/B− и M+/M−, гребёнка 2 × 4</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6N137 ×2 с резисторами и подтяжками, реле NRP-15-A-24D + диод E-099, шлейф 5 проводов (разъём E-098)</t>
+        </is>
       </c>
       <c r="G6" s="2">
         <f>IFERROR(INDEX(Компоненты!$L:$L,MATCH(A6,Компоненты!$A:$A,0)),"")</f>
@@ -6579,16 +6847,16 @@
         <f>IFERROR(INDEX(Компоненты!$R:$R,MATCH(A6,Компоненты!$A:$A,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>130</v>
-      </c>
+      <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>344</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACS712-30A модуль</t>
+        </is>
       </c>
       <c r="C7" s="2" t="s">
         <v>126</v>
@@ -6596,8 +6864,10 @@
       <c r="D7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>345</v>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACS712ELCTR-30A, фильтр, клеммник</t>
+        </is>
       </c>
       <c r="F7" s="2" t="s">
         <v>346</v>
@@ -6614,9 +6884,7 @@
         <f>IFERROR(INDEX(Компоненты!$R:$R,MATCH(A7,Компоненты!$A:$A,0)),"")</f>
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>164</v>
-      </c>
+      <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -6975,8 +7243,10 @@
       <c r="D13" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>406</v>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Под 4,5 А ном. / ~20 А стоп. не проходят DRV8871, HF49FD 5 А, БП 200 Вт. Пересмотрено 20.10.2026: в ветке motor-fga FGA утверждён (E-041) вместе с IBT-2, NRP-15-A-24D, ACS712-30A, LRS-600-24</t>
+        </is>
       </c>
       <c r="F13" s="7" t="s">
         <v>361</v>

--- a/bom/Component_Base.xlsx
+++ b/bom/Component_Base.xlsx
@@ -1694,8 +1694,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Components" displayName="Components" ref="A1:V67" totalsRowShown="0">
-  <autoFilter ref="A1:V67" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Components" displayName="Components" ref="A1:V69" totalsRowShown="0">
+  <autoFilter ref="A1:V69" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Узел"/>
@@ -1937,7 +1937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V67"/>
+  <dimension ref="A1:V69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вариант motor-fga: расчётный ток стенда ≈ 21 А (4 × 4,5 А FGA + схват 2 А + логика ~0,9 А), запас ~16 %. 220 В доходит до блока: размещение (внутри стенда или отдельный бокс с PE) требует решения — «ноутбучная» схема в этом варианте не действует. Вход блока — клеммы под сетевой провод. Пусковой ток FGA ограничивать в ПО (разгон ШИМ, отключение по ACS712). Цену уточнить. Было (main): GST220A24-R7B, 9,2 А.</t>
+          <t xml:space="preserve">Вариант motor-fga: расчётный ток стенда ≈ 21 А (4 × 4,5 А FGA + схват 2 А + логика ~0,9 А), запас ~16 %. Размещение — снаружи стенда, в отдельном корпусе E-101 (решение Mikhail 20.10.2026): 220 В в стенд не заходит. Сеть — через разъём C14 с предохранителем (тип T) и выключателем E-102, шнур E-016; клемма FG блока — на PE. Переключатель 115/230 В выставить на 230 В до первого включения. Выход — кабель 12 AWG, 1,5 м, с вилкой XT60 (E-014). При перегрузке 105–150 % блок ограничивает ток и отключается до повторной подачи сети: в ПО плавный разгон ШИМ, разнесённый пуск моторов, отключение по ACS712. Цену уточнить. Было (main): GST220A24-R7B, 9,2 А.</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вариант motor-fga: KPJX-PM-4S (2 × 7,5 А = 15 А) не проходит по току 21–25 А. Кабель блок питания → корпус 12 AWG. Было (main): Kycon KPJX-PM-4S.</t>
+          <t xml:space="preserve">Вариант motor-fga: блок питания снаружи (решение 20.10.2026) — гнездо XT60 на корпусе стенда, вилка на кабеле блока, кабель 12 AWG, 1,5 м (падение ~0,4 В при 21 А). KPJX-PM-4S (2 × 7,5 А = 15 А) не проходит по току 21–25 А. Было (main): Kycon KPJX-PM-4S.</t>
         </is>
       </c>
     </row>
@@ -5674,8 +5674,10 @@
       <c r="B56" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>288</v>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сетевой шнур блока питания (Schuko — IEC C13)</t>
+        </is>
       </c>
       <c r="D56" s="2" t="s">
         <v>37</v>
@@ -5727,12 +5729,14 @@
       <c r="T56" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="U56" s="2" t="s">
-        <v>268</v>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вход адаптера GST220A — C14, шнур в комплект не входит; ток от сети ~1 А. Вариант motor-fga: у LRS-600-24 вход — клеммы, шнур C13 не подходит; сетевой провод 3 × 0,75–1 мм² с вилкой — уточнить вместе с размещением блока. Цена не заполнена</t>
+          <t xml:space="preserve">Вход адаптера GST220A — C14, шнур в комплект не входит. Вариант motor-fga: вход корпуса блока E-101 — разъём C14 (E-102), шнур C13 подходит; ток из сети до ~7,5 А при полной нагрузке — 3 × 0,75 мм² (10 А) проходит, лучше 3 × 1,0 мм². Цена не заполнена</t>
         </is>
       </c>
     </row>
@@ -6504,6 +6508,178 @@
       <c r="V67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Вариант motor-fga: ввод +24 на PS (X1), ток 21–25 А: контакты 1, 2 — +24V_IN, 3, 4 — GND_P (2 × 15 А на полюс), провод 2 × 1,5 мм² на полюс. Тип — как клеммник на модуле IBT-2 (фото Mikhail 20.10.2026); наличие 4-контактного исполнения сверить. Выходы X6…X10 — DG301-5.0-02P (E-017).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-101</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Питание</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корпус блока питания (снаружи стенда)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Компонент</t>
+        </is>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Корпус под LRS-600-24 (225 × 124 × 41 мм) с вентиляционными отверстиями — модель требует подбора</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только функция</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Утверждено</t>
+        </is>
+      </c>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2">
+        <v>1</v>
+      </c>
+      <c r="K68" s="2">
+        <v>1</v>
+      </c>
+      <c r="L68" s="2">
+        <f>J68*K68</f>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Силовая</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>0</v>
+      </c>
+      <c r="R68" s="2">
+        <f>IF(D68="Внутри модуля",0,MAX(0,L68-Q68))</f>
+      </c>
+      <c r="S68" s="2">
+        <f>R68*P68</f>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Да</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вариант motor-fga: блок питания снаружи стенда (решение Mikhail 20.10.2026). Внутри: LRS-600-24, разъём C14 E-102, PE на клемму FG и на металлические части корпуса, изоляция клемм 220 В, фиксация кабелей, проход воздуха для вентилятора блока.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-102</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Питание</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Сетевой разъём корпуса блока питания</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Компонент</t>
+        </is>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IEC C14 с держателем предохранителя и выключателем — модель и номинал предохранителя требуют подбора</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только функция</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Утверждено</t>
+        </is>
+      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2">
+        <v>1</v>
+      </c>
+      <c r="K69" s="2">
+        <v>1</v>
+      </c>
+      <c r="L69" s="2">
+        <f>J69*K69</f>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Силовая</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>0</v>
+      </c>
+      <c r="R69" s="2">
+        <f>IF(D69="Внутри модуля",0,MAX(0,L69-Q69))</f>
+      </c>
+      <c r="S69" s="2">
+        <f>R69*P69</f>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Нет</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">чат 20.10.2026 (утверждено Mikhail, ветка motor-fga)</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Вариант motor-fga: ток из сети ~7,5 А при 230 В и полной нагрузке, пусковой ~60 А — предохранитель с задержкой (тип T), номинал — по инструкции Mean Well.</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6858,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разъём XT60 E-014, предохранитель 25 А E-003, реле E-013 + диод E-015, кнопка E-002</t>
+          <t xml:space="preserve">Разъём XT60 E-014, предохранитель 25 А E-003, реле E-013 + диод E-015, кнопка E-002; блок — снаружи стенда в корпусе E-101, сеть через C14 E-102</t>
         </is>
       </c>
       <c r="G2" s="2">
